--- a/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2021_2024_raw.xlsx
+++ b/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2021_2024_raw.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vasilauskas\GitHub\EV-Transition\data\processed\sam_auto_dashboard_2024_refresh\occ_change_by_education\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3743E46-AC60-4AE6-9998-957AF6515D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
     <sheet name="Education+Training" sheetId="2" r:id="rId2"/>
     <sheet name="Edu+Training (custom)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -120,13 +114,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,13 +125,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -182,47 +164,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -260,7 +222,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -294,7 +256,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -329,10 +290,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,16 +465,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="7" max="8" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="5"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,20 +488,20 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -565,20 +520,20 @@
       <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>11960</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2">
         <v>11795.49449630758</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2">
         <v>-164.5055036924241</v>
       </c>
-      <c r="J2" s="5">
-        <v>-1.3754640776958539E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <v>-0.01375464077695854</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -597,20 +552,20 @@
       <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>55220</v>
       </c>
-      <c r="H3" s="3">
-        <v>57389.228368399163</v>
-      </c>
-      <c r="I3" s="3">
+      <c r="H3">
+        <v>57389.22836839916</v>
+      </c>
+      <c r="I3">
         <v>2169.228368399155</v>
       </c>
-      <c r="J3" s="5">
-        <v>3.9283382260035409E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <v>0.03928338226003541</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -629,20 +584,20 @@
       <c r="F4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>2990</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>3419.27713529327</v>
       </c>
-      <c r="I4" s="3">
-        <v>429.27713529326962</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="I4">
+        <v>429.2771352932696</v>
+      </c>
+      <c r="J4">
         <v>0.1435709482586186</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -661,20 +616,20 @@
       <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>11390</v>
       </c>
-      <c r="H5" s="3">
-        <v>12673.950381679369</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1283.9503816793681</v>
-      </c>
-      <c r="J5" s="5">
+      <c r="H5">
+        <v>12673.95038167937</v>
+      </c>
+      <c r="I5">
+        <v>1283.950381679368</v>
+      </c>
+      <c r="J5">
         <v>0.1127261090148699</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -693,20 +648,20 @@
       <c r="F6" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>28480</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6">
         <v>29602.79898218832</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6">
         <v>1122.798982188317</v>
       </c>
-      <c r="J6" s="5">
-        <v>3.9424121565601003E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J6">
+        <v>0.039424121565601</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -725,20 +680,20 @@
       <c r="F7" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>6210</v>
       </c>
-      <c r="H7" s="3">
-        <v>5273.2506361323149</v>
-      </c>
-      <c r="I7" s="3">
-        <v>-936.74936386768513</v>
-      </c>
-      <c r="J7" s="5">
-        <v>-0.15084530819125361</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <v>5273.250636132315</v>
+      </c>
+      <c r="I7">
+        <v>-936.7493638676851</v>
+      </c>
+      <c r="J7">
+        <v>-0.1508453081912536</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -757,20 +712,20 @@
       <c r="F8" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>1800</v>
       </c>
-      <c r="H8" s="3">
-        <v>2072.9108040200931</v>
-      </c>
-      <c r="I8" s="3">
-        <v>272.91080402009271</v>
-      </c>
-      <c r="J8" s="5">
+      <c r="H8">
+        <v>2072.910804020093</v>
+      </c>
+      <c r="I8">
+        <v>272.9108040200927</v>
+      </c>
+      <c r="J8">
         <v>0.1516171133444959</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -789,20 +744,20 @@
       <c r="F9" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>11440</v>
       </c>
-      <c r="H9" s="3">
-        <v>13525.229899497501</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2085.2298994974972</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0.18227534086516581</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <v>13525.2298994975</v>
+      </c>
+      <c r="I9">
+        <v>2085.229899497497</v>
+      </c>
+      <c r="J9">
+        <v>0.1822753408651658</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -821,20 +776,20 @@
       <c r="F10" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>790</v>
       </c>
-      <c r="H10" s="3">
-        <v>738.85929648241051</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-51.140703517589493</v>
-      </c>
-      <c r="J10" s="5">
-        <v>-6.4735067743784167E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H10">
+        <v>738.8592964824105</v>
+      </c>
+      <c r="I10">
+        <v>-51.14070351758949</v>
+      </c>
+      <c r="J10">
+        <v>-0.06473506774378417</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -853,20 +808,20 @@
       <c r="F11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>7700</v>
       </c>
-      <c r="H11" s="3">
-        <v>8607.4536122409099</v>
-      </c>
-      <c r="I11" s="3">
-        <v>907.45361224090993</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0.11785111847284541</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H11">
+        <v>8607.45361224091</v>
+      </c>
+      <c r="I11">
+        <v>907.4536122409099</v>
+      </c>
+      <c r="J11">
+        <v>0.1178511184728454</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -885,20 +840,20 @@
       <c r="F12" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>35530</v>
       </c>
-      <c r="H12" s="3">
-        <v>39178.080573310137</v>
-      </c>
-      <c r="I12" s="3">
-        <v>3648.0805733101438</v>
-      </c>
-      <c r="J12" s="5">
+      <c r="H12">
+        <v>39178.08057331014</v>
+      </c>
+      <c r="I12">
+        <v>3648.080573310144</v>
+      </c>
+      <c r="J12">
         <v>0.1026760645457401</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -917,20 +872,20 @@
       <c r="F13" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>2380</v>
       </c>
-      <c r="H13" s="3">
-        <v>2657.4658144489508</v>
-      </c>
-      <c r="I13" s="3">
-        <v>277.46581444895128</v>
-      </c>
-      <c r="J13" s="5">
+      <c r="H13">
+        <v>2657.465814448951</v>
+      </c>
+      <c r="I13">
+        <v>277.4658144489513</v>
+      </c>
+      <c r="J13">
         <v>0.116582274978551</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -949,20 +904,20 @@
       <c r="F14" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>4810</v>
       </c>
-      <c r="H14" s="3">
-        <v>7463.3777224642181</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2653.3777224642181</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0.55163778013809106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H14">
+        <v>7463.377722464218</v>
+      </c>
+      <c r="I14">
+        <v>2653.377722464218</v>
+      </c>
+      <c r="J14">
+        <v>0.5516377801380911</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -981,20 +936,20 @@
       <c r="F15" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>9360</v>
       </c>
-      <c r="H15" s="3">
-        <v>9772.9290603609261</v>
-      </c>
-      <c r="I15" s="3">
-        <v>412.92906036092609</v>
-      </c>
-      <c r="J15" s="5">
-        <v>4.4116352602663042E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <v>9772.929060360926</v>
+      </c>
+      <c r="I15">
+        <v>412.9290603609261</v>
+      </c>
+      <c r="J15">
+        <v>0.04411635260266304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1013,20 +968,20 @@
       <c r="F16" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16">
         <v>560</v>
       </c>
-      <c r="H16" s="3">
-        <v>1046.6932171748549</v>
-      </c>
-      <c r="I16" s="3">
-        <v>486.69321717485542</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0.86909503066938454</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <v>1046.693217174855</v>
+      </c>
+      <c r="I16">
+        <v>486.6932171748554</v>
+      </c>
+      <c r="J16">
+        <v>0.8690950306693845</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1045,20 +1000,20 @@
       <c r="F17" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>83510</v>
       </c>
-      <c r="H17" s="3">
-        <v>85951.422745735385</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="H17">
+        <v>85951.42274573538</v>
+      </c>
+      <c r="I17">
         <v>2441.422745735385</v>
       </c>
-      <c r="J17" s="5">
-        <v>2.9235094548382041E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17">
+        <v>0.02923509454838204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -1077,20 +1032,20 @@
       <c r="F18" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18">
         <v>19910</v>
       </c>
-      <c r="H18" s="3">
-        <v>23289.495938261451</v>
-      </c>
-      <c r="I18" s="3">
-        <v>3379.4959382614538</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0.16973862070625079</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <v>23289.49593826145</v>
+      </c>
+      <c r="I18">
+        <v>3379.495938261454</v>
+      </c>
+      <c r="J18">
+        <v>0.1697386207062508</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1109,20 +1064,20 @@
       <c r="F19" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>12300</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19">
         <v>10966.08131600317</v>
       </c>
-      <c r="I19" s="3">
-        <v>-1333.9186839968299</v>
-      </c>
-      <c r="J19" s="5">
+      <c r="I19">
+        <v>-1333.91868399683</v>
+      </c>
+      <c r="J19">
         <v>-0.1084486734956772</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1141,20 +1096,20 @@
       <c r="F20" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20">
         <v>24380</v>
       </c>
-      <c r="H20" s="3">
-        <v>28420.738487972219</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="H20">
+        <v>28420.73848797222</v>
+      </c>
+      <c r="I20">
         <v>4040.738487972219</v>
       </c>
-      <c r="J20" s="5">
-        <v>0.16573988876014031</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20">
+        <v>0.1657398887601403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1173,20 +1128,20 @@
       <c r="F21" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21">
         <v>135650</v>
       </c>
-      <c r="H21" s="3">
-        <v>136344.20549828219</v>
-      </c>
-      <c r="I21" s="3">
-        <v>694.20549828218645</v>
-      </c>
-      <c r="J21" s="5">
-        <v>5.117622545390243E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H21">
+        <v>136344.2054982822</v>
+      </c>
+      <c r="I21">
+        <v>694.2054982821865</v>
+      </c>
+      <c r="J21">
+        <v>0.005117622545390243</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1205,20 +1160,20 @@
       <c r="F22" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>8130</v>
       </c>
-      <c r="H22" s="3">
-        <v>8317.0560137456159</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="H22">
+        <v>8317.056013745616</v>
+      </c>
+      <c r="I22">
         <v>187.0560137456159</v>
       </c>
-      <c r="J22" s="5">
-        <v>2.3008119771908479E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22">
+        <v>0.02300811977190848</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1237,20 +1192,20 @@
       <c r="F23" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23">
         <v>15400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23">
         <v>19646.96893063571</v>
       </c>
-      <c r="I23" s="3">
-        <v>4246.9689306357141</v>
-      </c>
-      <c r="J23" s="5">
+      <c r="I23">
+        <v>4246.968930635714</v>
+      </c>
+      <c r="J23">
         <v>0.2757772032880334</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1269,20 +1224,20 @@
       <c r="F24" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24">
         <v>77320</v>
       </c>
-      <c r="H24" s="3">
-        <v>87775.906791907677</v>
-      </c>
-      <c r="I24" s="3">
-        <v>10455.906791907681</v>
-      </c>
-      <c r="J24" s="5">
+      <c r="H24">
+        <v>87775.90679190768</v>
+      </c>
+      <c r="I24">
+        <v>10455.90679190768</v>
+      </c>
+      <c r="J24">
         <v>0.1352290066206373</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1301,20 +1256,20 @@
       <c r="F25" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25">
         <v>7900</v>
       </c>
-      <c r="H25" s="3">
-        <v>7917.1242774566126</v>
-      </c>
-      <c r="I25" s="3">
-        <v>17.124277456612621</v>
-      </c>
-      <c r="J25" s="5">
-        <v>2.1676300577990648E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H25">
+        <v>7917.124277456613</v>
+      </c>
+      <c r="I25">
+        <v>17.12427745661262</v>
+      </c>
+      <c r="J25">
+        <v>0.002167630057799065</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1333,20 +1288,20 @@
       <c r="F26" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>4600</v>
       </c>
-      <c r="H26" s="3">
-        <v>6147.4420638390802</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="H26">
+        <v>6147.44206383908</v>
+      </c>
+      <c r="I26">
         <v>1547.44206383908</v>
       </c>
-      <c r="J26" s="5">
-        <v>0.33640044866066959</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26">
+        <v>0.3364004486606696</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1365,20 +1320,20 @@
       <c r="F27" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27">
         <v>43860</v>
       </c>
-      <c r="H27" s="3">
-        <v>45578.312199387823</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="H27">
+        <v>45578.31219938782</v>
+      </c>
+      <c r="I27">
         <v>1718.312199387816</v>
       </c>
-      <c r="J27" s="5">
-        <v>3.9177204728404372E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27">
+        <v>0.03917720472840437</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1397,20 +1352,20 @@
       <c r="F28" t="s">
         <v>25</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28">
         <v>16000</v>
       </c>
-      <c r="H28" s="3">
-        <v>17874.245736773111</v>
-      </c>
-      <c r="I28" s="3">
-        <v>1874.2457367731081</v>
-      </c>
-      <c r="J28" s="5">
+      <c r="H28">
+        <v>17874.24573677311</v>
+      </c>
+      <c r="I28">
+        <v>1874.245736773108</v>
+      </c>
+      <c r="J28">
         <v>0.1171403585483192</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1429,20 +1384,20 @@
       <c r="F29" t="s">
         <v>23</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29">
         <v>1650</v>
       </c>
-      <c r="H29" s="3">
-        <v>3914.0732538330271</v>
-      </c>
-      <c r="I29" s="3">
-        <v>2264.0732538330271</v>
-      </c>
-      <c r="J29" s="5">
-        <v>1.3721656083836531</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <v>3914.073253833027</v>
+      </c>
+      <c r="I29">
+        <v>2264.073253833027</v>
+      </c>
+      <c r="J29">
+        <v>1.372165608383653</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1461,20 +1416,20 @@
       <c r="F30" t="s">
         <v>24</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30">
         <v>14360</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30">
         <v>15786.09646507664</v>
       </c>
-      <c r="I30" s="3">
-        <v>1426.0964650766359</v>
-      </c>
-      <c r="J30" s="5">
-        <v>9.9310338793637626E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I30">
+        <v>1426.096465076636</v>
+      </c>
+      <c r="J30">
+        <v>0.09931033879363763</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1493,17 +1448,17 @@
       <c r="F31" t="s">
         <v>25</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31">
         <v>29060</v>
       </c>
-      <c r="H31" s="3">
-        <v>27188.830281090341</v>
-      </c>
-      <c r="I31" s="3">
+      <c r="H31">
+        <v>27188.83028109034</v>
+      </c>
+      <c r="I31">
         <v>-1871.169718909659</v>
       </c>
-      <c r="J31" s="5">
-        <v>-6.4389873327930475E-2</v>
+      <c r="J31">
+        <v>-0.06438987332793047</v>
       </c>
     </row>
   </sheetData>
@@ -1512,11 +1467,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1548,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1577,10 +1532,10 @@
         <v>-164.5055036924241</v>
       </c>
       <c r="J2">
-        <v>-1.3754640776958539E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.01375464077695854</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1606,13 +1561,13 @@
         <v>15083.26097255121</v>
       </c>
       <c r="I3">
-        <v>303.26097255121022</v>
+        <v>303.2609725512102</v>
       </c>
       <c r="J3">
-        <v>2.0518333731475661E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02051833373147566</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1635,16 +1590,16 @@
         <v>43430</v>
       </c>
       <c r="H4">
-        <v>45725.244531141223</v>
+        <v>45725.24453114122</v>
       </c>
       <c r="I4">
-        <v>2295.2445311412162</v>
+        <v>2295.244531141216</v>
       </c>
       <c r="J4">
-        <v>5.2849286924734423E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.05284928692473442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1667,16 +1622,16 @@
         <v>11390</v>
       </c>
       <c r="H5">
-        <v>12673.950381679369</v>
+        <v>12673.95038167937</v>
       </c>
       <c r="I5">
-        <v>1283.9503816793681</v>
+        <v>1283.950381679368</v>
       </c>
       <c r="J5">
         <v>0.1127261090148699</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1699,16 +1654,16 @@
         <v>6460</v>
       </c>
       <c r="H6">
-        <v>6513.4223918575044</v>
+        <v>6513.422391857504</v>
       </c>
       <c r="I6">
-        <v>53.422391857504408</v>
+        <v>53.42239185750441</v>
       </c>
       <c r="J6">
-        <v>8.269720101780868E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.008269720101780868</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1734,13 +1689,13 @@
         <v>28362.62722646313</v>
       </c>
       <c r="I7">
-        <v>132.62722646312611</v>
+        <v>132.6272264631261</v>
       </c>
       <c r="J7">
-        <v>4.6980951634121903E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.00469809516341219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1763,16 +1718,16 @@
         <v>1800</v>
       </c>
       <c r="H8">
-        <v>2072.9108040200931</v>
+        <v>2072.910804020093</v>
       </c>
       <c r="I8">
-        <v>272.91080402009271</v>
+        <v>272.9108040200927</v>
       </c>
       <c r="J8">
         <v>0.1516171133444959</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1795,7 +1750,7 @@
         <v>2350</v>
       </c>
       <c r="H9">
-        <v>2883.6036432160799</v>
+        <v>2883.60364321608</v>
       </c>
       <c r="I9">
         <v>533.6036432160804</v>
@@ -1804,7 +1759,7 @@
         <v>0.2270653800919491</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1833,10 +1788,10 @@
         <v>1500.485552763826</v>
       </c>
       <c r="J10">
-        <v>0.15187100736475981</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.1518710073647598</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1859,16 +1814,16 @@
         <v>7700</v>
       </c>
       <c r="H11">
-        <v>8607.4536122409099</v>
+        <v>8607.45361224091</v>
       </c>
       <c r="I11">
-        <v>907.45361224090993</v>
+        <v>907.4536122409099</v>
       </c>
       <c r="J11">
-        <v>0.11785111847284541</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.1178511184728454</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1891,16 +1846,16 @@
         <v>7880</v>
       </c>
       <c r="H12">
-        <v>8001.7077280650738</v>
+        <v>8001.707728065074</v>
       </c>
       <c r="I12">
-        <v>121.70772806507379</v>
+        <v>121.7077280650738</v>
       </c>
       <c r="J12">
-        <v>1.5445143155466211E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.01544514315546621</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1923,16 +1878,16 @@
         <v>30030</v>
       </c>
       <c r="H13">
-        <v>33833.838659694018</v>
+        <v>33833.83865969402</v>
       </c>
       <c r="I13">
-        <v>3803.8386596940181</v>
+        <v>3803.838659694018</v>
       </c>
       <c r="J13">
-        <v>0.12666795403576481</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.1266679540357648</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1955,16 +1910,16 @@
         <v>4810</v>
       </c>
       <c r="H14">
-        <v>7463.3777224642181</v>
+        <v>7463.377722464218</v>
       </c>
       <c r="I14">
-        <v>2653.3777224642181</v>
+        <v>2653.377722464218</v>
       </c>
       <c r="J14">
-        <v>0.55163778013809106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.5516377801380911</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1987,16 +1942,16 @@
         <v>2300</v>
       </c>
       <c r="H15">
-        <v>2355.0597386434288</v>
+        <v>2355.059738643429</v>
       </c>
       <c r="I15">
-        <v>55.059738643429228</v>
+        <v>55.05973864342923</v>
       </c>
       <c r="J15">
-        <v>2.3939016801490971E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02393901680149097</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -2019,16 +1974,16 @@
         <v>7620</v>
       </c>
       <c r="H16">
-        <v>8464.5625388923509</v>
+        <v>8464.562538892351</v>
       </c>
       <c r="I16">
-        <v>844.56253889235086</v>
+        <v>844.5625388923509</v>
       </c>
       <c r="J16">
         <v>0.1108349788572639</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -2051,16 +2006,16 @@
         <v>83510</v>
       </c>
       <c r="H17">
-        <v>85951.422745735385</v>
+        <v>85951.42274573538</v>
       </c>
       <c r="I17">
         <v>2441.422745735385</v>
       </c>
       <c r="J17">
-        <v>2.9235094548382041E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02923509454838204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2083,16 +2038,16 @@
         <v>7230</v>
       </c>
       <c r="H18">
-        <v>8964.2588139723084</v>
+        <v>8964.258813972308</v>
       </c>
       <c r="I18">
         <v>1734.258813972308</v>
       </c>
       <c r="J18">
-        <v>0.23986982212618371</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.2398698221261837</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -2115,16 +2070,16 @@
         <v>24980</v>
       </c>
       <c r="H19">
-        <v>25291.318440292322</v>
+        <v>25291.31844029232</v>
       </c>
       <c r="I19">
-        <v>311.31844029231797</v>
+        <v>311.318440292318</v>
       </c>
       <c r="J19">
-        <v>1.246270777791505E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.01246270777791505</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2147,16 +2102,16 @@
         <v>24380</v>
       </c>
       <c r="H20">
-        <v>28420.738487972219</v>
+        <v>28420.73848797222</v>
       </c>
       <c r="I20">
         <v>4040.738487972219</v>
       </c>
       <c r="J20">
-        <v>0.16573988876014031</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.1657398887601403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2179,16 +2134,16 @@
         <v>18310</v>
       </c>
       <c r="H21">
-        <v>19251.159450171741</v>
+        <v>19251.15945017174</v>
       </c>
       <c r="I21">
         <v>941.1594501717409</v>
       </c>
       <c r="J21">
-        <v>5.1401389960226147E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.05140138996022615</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -2214,13 +2169,13 @@
         <v>125410.102061856</v>
       </c>
       <c r="I22">
-        <v>-59.897938143956708</v>
+        <v>-59.89793814395671</v>
       </c>
       <c r="J22">
-        <v>-4.7738852430028459E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.0004773885243002846</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -2246,13 +2201,13 @@
         <v>19646.96893063571</v>
       </c>
       <c r="I23">
-        <v>4246.9689306357141</v>
+        <v>4246.968930635714</v>
       </c>
       <c r="J23">
         <v>0.2757772032880334</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -2275,16 +2230,16 @@
         <v>51050</v>
       </c>
       <c r="H24">
-        <v>60774.346098266084</v>
+        <v>60774.34609826608</v>
       </c>
       <c r="I24">
-        <v>9724.3460982660836</v>
+        <v>9724.346098266084</v>
       </c>
       <c r="J24">
-        <v>0.19048670123929651</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.1904867012392965</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -2307,16 +2262,16 @@
         <v>34170</v>
       </c>
       <c r="H25">
-        <v>34918.684971098213</v>
+        <v>34918.68497109821</v>
       </c>
       <c r="I25">
-        <v>748.68497109821328</v>
+        <v>748.6849710982133</v>
       </c>
       <c r="J25">
-        <v>2.1910593242558191E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02191059324255819</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -2339,16 +2294,16 @@
         <v>4600</v>
       </c>
       <c r="H26">
-        <v>6147.4420638390802</v>
+        <v>6147.44206383908</v>
       </c>
       <c r="I26">
         <v>1547.44206383908</v>
       </c>
       <c r="J26">
-        <v>0.33640044866066959</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.3364004486606696</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -2371,16 +2326,16 @@
         <v>34400</v>
       </c>
       <c r="H27">
-        <v>34734.062090074352</v>
+        <v>34734.06209007435</v>
       </c>
       <c r="I27">
-        <v>334.06209007435251</v>
+        <v>334.0620900743525</v>
       </c>
       <c r="J27">
-        <v>9.7111072696032686E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.009711107269603269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -2403,16 +2358,16 @@
         <v>25460</v>
       </c>
       <c r="H28">
-        <v>28718.495846086571</v>
+        <v>28718.49584608657</v>
       </c>
       <c r="I28">
-        <v>3258.4958460865669</v>
+        <v>3258.495846086567</v>
       </c>
       <c r="J28">
-        <v>0.12798491147237109</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.1279849114723711</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2435,16 +2390,16 @@
         <v>1650</v>
       </c>
       <c r="H29">
-        <v>3914.0732538330271</v>
+        <v>3914.073253833027</v>
       </c>
       <c r="I29">
-        <v>2264.0732538330271</v>
+        <v>2264.073253833027</v>
       </c>
       <c r="J29">
-        <v>1.3721656083836531</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1.372165608383653</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -2467,16 +2422,16 @@
         <v>9880</v>
       </c>
       <c r="H30">
-        <v>10643.882879045979</v>
+        <v>10643.88287904598</v>
       </c>
       <c r="I30">
         <v>763.8828790459811</v>
       </c>
       <c r="J30">
-        <v>7.7316080875099308E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.07731608087509931</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -2499,13 +2454,13 @@
         <v>33540</v>
       </c>
       <c r="H31">
-        <v>32331.043867120999</v>
+        <v>32331.043867121</v>
       </c>
       <c r="I31">
-        <v>-1208.9561328790039</v>
+        <v>-1208.956132879004</v>
       </c>
       <c r="J31">
-        <v>-3.6045203723285762E-2</v>
+        <v>-0.03604520372328576</v>
       </c>
     </row>
   </sheetData>
@@ -2514,16 +2469,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="7" max="8" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="5"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2542,20 +2492,20 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2574,20 +2524,20 @@
       <c r="F2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>920</v>
       </c>
-      <c r="H2" s="3">
-        <v>1224.0607496168191</v>
-      </c>
-      <c r="I2" s="3">
-        <v>304.06074961681912</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0.33050081480089027</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>1224.060749616819</v>
+      </c>
+      <c r="I2">
+        <v>304.0607496168191</v>
+      </c>
+      <c r="J2">
+        <v>0.3305008148008903</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2606,20 +2556,20 @@
       <c r="F3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>11960</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <v>11795.49449630758</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3">
         <v>-164.5055036924241</v>
       </c>
-      <c r="J3" s="5">
-        <v>-1.3754640776958539E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <v>-0.01375464077695854</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2638,20 +2588,20 @@
       <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>41910</v>
       </c>
-      <c r="H4" s="3">
-        <v>43782.933259021971</v>
-      </c>
-      <c r="I4" s="3">
+      <c r="H4">
+        <v>43782.93325902197</v>
+      </c>
+      <c r="I4">
         <v>1872.933259021971</v>
       </c>
-      <c r="J4" s="5">
-        <v>4.4689412050154413E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J4">
+        <v>0.04468941205015441</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2670,20 +2620,20 @@
       <c r="F5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>15380</v>
       </c>
-      <c r="H5" s="3">
-        <v>15801.511495053641</v>
-      </c>
-      <c r="I5" s="3">
-        <v>421.51149505363901</v>
-      </c>
-      <c r="J5" s="5">
-        <v>2.7406469119222301E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>15801.51149505364</v>
+      </c>
+      <c r="I5">
+        <v>421.511495053639</v>
+      </c>
+      <c r="J5">
+        <v>0.0274064691192223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2702,20 +2652,20 @@
       <c r="F6" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>670</v>
       </c>
-      <c r="H6" s="3">
-        <v>836.86386768447176</v>
-      </c>
-      <c r="I6" s="3">
-        <v>166.86386768447181</v>
-      </c>
-      <c r="J6" s="5">
+      <c r="H6">
+        <v>836.8638676844718</v>
+      </c>
+      <c r="I6">
+        <v>166.8638676844718</v>
+      </c>
+      <c r="J6">
         <v>0.2490505487827937</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2734,20 +2684,20 @@
       <c r="F7" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>11390</v>
       </c>
-      <c r="H7" s="3">
-        <v>12673.950381679369</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1283.9503816793681</v>
-      </c>
-      <c r="J7" s="5">
+      <c r="H7">
+        <v>12673.95038167937</v>
+      </c>
+      <c r="I7">
+        <v>1283.950381679368</v>
+      </c>
+      <c r="J7">
         <v>0.1127261090148699</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2766,20 +2716,20 @@
       <c r="F8" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>27150</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <v>27283.77862595423</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8">
         <v>133.7786259542336</v>
       </c>
-      <c r="J8" s="5">
-        <v>4.9273895379091546E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8">
+        <v>0.004927389537909155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2798,20 +2748,20 @@
       <c r="F9" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>6870</v>
       </c>
-      <c r="H9" s="3">
-        <v>6755.4071246819267</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="H9">
+        <v>6755.407124681927</v>
+      </c>
+      <c r="I9">
         <v>-114.5928753180733</v>
       </c>
-      <c r="J9" s="5">
-        <v>-1.668018563581853E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9">
+        <v>-0.01668018563581853</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2830,20 +2780,20 @@
       <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>50</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10">
         <v>123.1432160804015</v>
       </c>
-      <c r="I10" s="3">
-        <v>73.143216080401473</v>
-      </c>
-      <c r="J10" s="5">
+      <c r="I10">
+        <v>73.14321608040147</v>
+      </c>
+      <c r="J10">
         <v>1.462864321608029</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2862,20 +2812,20 @@
       <c r="F11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>1800</v>
       </c>
-      <c r="H11" s="3">
-        <v>2072.9108040200931</v>
-      </c>
-      <c r="I11" s="3">
-        <v>272.91080402009271</v>
-      </c>
-      <c r="J11" s="5">
+      <c r="H11">
+        <v>2072.910804020093</v>
+      </c>
+      <c r="I11">
+        <v>272.9108040200927</v>
+      </c>
+      <c r="J11">
         <v>0.1516171133444959</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2894,20 +2844,20 @@
       <c r="F12" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>9740</v>
       </c>
-      <c r="H12" s="3">
-        <v>11195.770728643231</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1455.7707286432251</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0.14946311382373981</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <v>11195.77072864323</v>
+      </c>
+      <c r="I12">
+        <v>1455.770728643225</v>
+      </c>
+      <c r="J12">
+        <v>0.1494631138237398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -2926,20 +2876,20 @@
       <c r="F13" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>2440</v>
       </c>
-      <c r="H13" s="3">
-        <v>2945.1752512562812</v>
-      </c>
-      <c r="I13" s="3">
-        <v>505.17525125628117</v>
-      </c>
-      <c r="J13" s="5">
+      <c r="H13">
+        <v>2945.175251256281</v>
+      </c>
+      <c r="I13">
+        <v>505.1752512562812</v>
+      </c>
+      <c r="J13">
         <v>0.2070390374001152</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -2958,20 +2908,20 @@
       <c r="F14" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>570</v>
       </c>
-      <c r="H14" s="3">
-        <v>869.53844663954158</v>
-      </c>
-      <c r="I14" s="3">
-        <v>299.53844663954158</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0.52550604673603785</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H14">
+        <v>869.5384466395416</v>
+      </c>
+      <c r="I14">
+        <v>299.5384466395416</v>
+      </c>
+      <c r="J14">
+        <v>0.5255060467360378</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -2990,20 +2940,20 @@
       <c r="F15" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>7700</v>
       </c>
-      <c r="H15" s="3">
-        <v>8607.4536122409099</v>
-      </c>
-      <c r="I15" s="3">
-        <v>907.45361224090993</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0.11785111847284541</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <v>8607.45361224091</v>
+      </c>
+      <c r="I15">
+        <v>907.4536122409099</v>
+      </c>
+      <c r="J15">
+        <v>0.1178511184728454</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -3022,20 +2972,20 @@
       <c r="F16" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16">
         <v>29200</v>
       </c>
-      <c r="H16" s="3">
-        <v>32680.967460778669</v>
-      </c>
-      <c r="I16" s="3">
-        <v>3480.9674607786692</v>
-      </c>
-      <c r="J16" s="5">
+      <c r="H16">
+        <v>32680.96746077867</v>
+      </c>
+      <c r="I16">
+        <v>3480.967460778669</v>
+      </c>
+      <c r="J16">
         <v>0.1192112144102284</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -3054,20 +3004,20 @@
       <c r="F17" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>8140</v>
       </c>
-      <c r="H17" s="3">
-        <v>8285.0404803408801</v>
-      </c>
-      <c r="I17" s="3">
-        <v>145.04048034088009</v>
-      </c>
-      <c r="J17" s="5">
-        <v>1.7818240828117948E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <v>8285.04048034088</v>
+      </c>
+      <c r="I17">
+        <v>145.0404803408801</v>
+      </c>
+      <c r="J17">
+        <v>0.01781824082811795</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -3086,20 +3036,20 @@
       <c r="F18" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18">
         <v>160</v>
       </c>
-      <c r="H18" s="3">
-        <v>602.98630989421156</v>
-      </c>
-      <c r="I18" s="3">
-        <v>442.98630989421162</v>
-      </c>
-      <c r="J18" s="5">
-        <v>2.7686644368388218</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <v>602.9863098942116</v>
+      </c>
+      <c r="I18">
+        <v>442.9863098942116</v>
+      </c>
+      <c r="J18">
+        <v>2.768664436838822</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -3118,20 +3068,20 @@
       <c r="F19" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>4810</v>
       </c>
-      <c r="H19" s="3">
-        <v>7463.3777224642181</v>
-      </c>
-      <c r="I19" s="3">
-        <v>2653.3777224642181</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0.55163778013809106</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H19">
+        <v>7463.377722464218</v>
+      </c>
+      <c r="I19">
+        <v>2653.377722464218</v>
+      </c>
+      <c r="J19">
+        <v>0.5516377801380911</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -3150,20 +3100,20 @@
       <c r="F20" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20">
         <v>7400</v>
       </c>
-      <c r="H20" s="3">
-        <v>7827.4449284380917</v>
-      </c>
-      <c r="I20" s="3">
-        <v>427.44492843809172</v>
-      </c>
-      <c r="J20" s="5">
-        <v>5.7762828167309682E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20">
+        <v>7827.444928438092</v>
+      </c>
+      <c r="I20">
+        <v>427.4449284380917</v>
+      </c>
+      <c r="J20">
+        <v>0.05776282816730968</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -3182,20 +3132,20 @@
       <c r="F21" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21">
         <v>2360</v>
       </c>
-      <c r="H21" s="3">
-        <v>2389.1910392034779</v>
-      </c>
-      <c r="I21" s="3">
-        <v>29.191039203477889</v>
-      </c>
-      <c r="J21" s="5">
-        <v>1.236908440825334E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H21">
+        <v>2389.191039203478</v>
+      </c>
+      <c r="I21">
+        <v>29.19103920347789</v>
+      </c>
+      <c r="J21">
+        <v>0.01236908440825334</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -3214,20 +3164,20 @@
       <c r="F22" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>9830</v>
       </c>
-      <c r="H22" s="3">
-        <v>8739.6640942322974</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="H22">
+        <v>8739.664094232297</v>
+      </c>
+      <c r="I22">
         <v>-1090.335905767703</v>
       </c>
-      <c r="J22" s="5">
-        <v>-0.11091921727036649</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22">
+        <v>-0.1109192172703665</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -3246,20 +3196,20 @@
       <c r="F23" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23">
         <v>83510</v>
       </c>
-      <c r="H23" s="3">
-        <v>85951.422745735385</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="H23">
+        <v>85951.42274573538</v>
+      </c>
+      <c r="I23">
         <v>2441.422745735385</v>
       </c>
-      <c r="J23" s="5">
-        <v>2.9235094548382041E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23">
+        <v>0.02923509454838204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -3278,20 +3228,20 @@
       <c r="F24" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24">
         <v>14290</v>
       </c>
-      <c r="H24" s="3">
-        <v>16063.404955320801</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="H24">
+        <v>16063.4049553208</v>
+      </c>
+      <c r="I24">
         <v>1773.404955320801</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24">
         <v>0.1241011165374948</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -3310,20 +3260,20 @@
       <c r="F25" t="s">
         <v>30</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25">
         <v>8090</v>
       </c>
-      <c r="H25" s="3">
-        <v>9452.5082047115266</v>
-      </c>
-      <c r="I25" s="3">
+      <c r="H25">
+        <v>9452.508204711527</v>
+      </c>
+      <c r="I25">
         <v>1362.508204711527</v>
       </c>
-      <c r="J25" s="5">
-        <v>0.16841881393220351</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25">
+        <v>0.1684188139322035</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -3342,20 +3292,20 @@
       <c r="F26" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>2670</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26">
         <v>2795.482474226756</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26">
         <v>125.4824742267556</v>
       </c>
-      <c r="J26" s="5">
-        <v>4.6997181358335423E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26">
+        <v>0.04699718135833542</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -3374,20 +3324,20 @@
       <c r="F27" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27">
         <v>24380</v>
       </c>
-      <c r="H27" s="3">
-        <v>28420.738487972219</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="H27">
+        <v>28420.73848797222</v>
+      </c>
+      <c r="I27">
         <v>4040.738487972219</v>
       </c>
-      <c r="J27" s="5">
-        <v>0.16573988876014031</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27">
+        <v>0.1657398887601403</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -3406,20 +3356,20 @@
       <c r="F28" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28">
         <v>122010</v>
       </c>
-      <c r="H28" s="3">
-        <v>122029.74914089389</v>
-      </c>
-      <c r="I28" s="3">
+      <c r="H28">
+        <v>122029.7491408939</v>
+      </c>
+      <c r="I28">
         <v>19.74914089392405</v>
       </c>
-      <c r="J28" s="5">
-        <v>1.6186493643081761E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28">
+        <v>0.0001618649364308176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -3438,20 +3388,20 @@
       <c r="F29" t="s">
         <v>30</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29">
         <v>19100</v>
       </c>
-      <c r="H29" s="3">
-        <v>19836.029896907119</v>
-      </c>
-      <c r="I29" s="3">
-        <v>736.02989690711911</v>
-      </c>
-      <c r="J29" s="5">
-        <v>3.8535596696707808E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <v>19836.02989690712</v>
+      </c>
+      <c r="I29">
+        <v>736.0298969071191</v>
+      </c>
+      <c r="J29">
+        <v>0.03853559669670781</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -3470,20 +3420,20 @@
       <c r="F30" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30">
         <v>210</v>
       </c>
-      <c r="H30" s="3">
-        <v>822.96423410401496</v>
-      </c>
-      <c r="I30" s="3">
-        <v>612.96423410401496</v>
-      </c>
-      <c r="J30" s="5">
-        <v>2.9188773052572139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H30">
+        <v>822.964234104015</v>
+      </c>
+      <c r="I30">
+        <v>612.964234104015</v>
+      </c>
+      <c r="J30">
+        <v>2.918877305257214</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -3502,20 +3452,20 @@
       <c r="F31" t="s">
         <v>23</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31">
         <v>15400</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31">
         <v>19646.96893063571</v>
       </c>
-      <c r="I31" s="3">
-        <v>4246.9689306357141</v>
-      </c>
-      <c r="J31" s="5">
+      <c r="I31">
+        <v>4246.968930635714</v>
+      </c>
+      <c r="J31">
         <v>0.2757772032880334</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -3534,20 +3484,20 @@
       <c r="F32" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32">
         <v>28370</v>
       </c>
-      <c r="H32" s="3">
-        <v>29126.683526011529</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="H32">
+        <v>29126.68352601153</v>
+      </c>
+      <c r="I32">
         <v>756.6835260115331</v>
       </c>
-      <c r="J32" s="5">
-        <v>2.6671960733575369E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J32">
+        <v>0.02667196073357537</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -3566,20 +3516,20 @@
       <c r="F33" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33">
         <v>56640</v>
       </c>
-      <c r="H33" s="3">
-        <v>65743.383309248748</v>
-      </c>
-      <c r="I33" s="3">
-        <v>9103.3833092487475</v>
-      </c>
-      <c r="J33" s="5">
-        <v>0.16072357537515439</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H33">
+        <v>65743.38330924875</v>
+      </c>
+      <c r="I33">
+        <v>9103.383309248748</v>
+      </c>
+      <c r="J33">
+        <v>0.1607235753751544</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -3598,17 +3548,17 @@
       <c r="F34" t="s">
         <v>28</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34">
         <v>0</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34">
         <v>50.72146917358625</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34">
         <v>50.72146917358625</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -3627,20 +3577,20 @@
       <c r="F35" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35">
         <v>4600</v>
       </c>
-      <c r="H35" s="3">
-        <v>6147.4420638390802</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="H35">
+        <v>6147.44206383908</v>
+      </c>
+      <c r="I35">
         <v>1547.44206383908</v>
       </c>
-      <c r="J35" s="5">
-        <v>0.33640044866066959</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J35">
+        <v>0.3364004486606696</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -3659,20 +3609,20 @@
       <c r="F36" t="s">
         <v>29</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36">
         <v>10540</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36">
         <v>12365.89418452115</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36">
         <v>1825.89418452115</v>
       </c>
-      <c r="J36" s="5">
-        <v>0.17323474236443551</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J36">
+        <v>0.1732347423644355</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -3691,20 +3641,20 @@
       <c r="F37" t="s">
         <v>30</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37">
         <v>49320</v>
       </c>
-      <c r="H37" s="3">
-        <v>51035.942282466181</v>
-      </c>
-      <c r="I37" s="3">
+      <c r="H37">
+        <v>51035.94228246618</v>
+      </c>
+      <c r="I37">
         <v>1715.942282466181</v>
       </c>
-      <c r="J37" s="5">
-        <v>3.4792017081633847E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J37">
+        <v>0.03479201708163385</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -3723,17 +3673,17 @@
       <c r="F38" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38">
         <v>0</v>
       </c>
-      <c r="H38" s="3">
-        <v>129.80344974446129</v>
-      </c>
-      <c r="I38" s="3">
-        <v>129.80344974446129</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H38">
+        <v>129.8034497444613</v>
+      </c>
+      <c r="I38">
+        <v>129.8034497444613</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -3752,20 +3702,20 @@
       <c r="F39" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39">
         <v>1650</v>
       </c>
-      <c r="H39" s="3">
-        <v>3914.0732538330271</v>
-      </c>
-      <c r="I39" s="3">
-        <v>2264.0732538330271</v>
-      </c>
-      <c r="J39" s="5">
-        <v>1.3721656083836531</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H39">
+        <v>3914.073253833027</v>
+      </c>
+      <c r="I39">
+        <v>2264.073253833027</v>
+      </c>
+      <c r="J39">
+        <v>1.372165608383653</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -3784,20 +3734,20 @@
       <c r="F40" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40">
         <v>4990</v>
       </c>
-      <c r="H40" s="3">
-        <v>5821.1854770016926</v>
-      </c>
-      <c r="I40" s="3">
-        <v>831.18547700169256</v>
-      </c>
-      <c r="J40" s="5">
-        <v>0.16657023587208269</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H40">
+        <v>5821.185477001693</v>
+      </c>
+      <c r="I40">
+        <v>831.1854770016926</v>
+      </c>
+      <c r="J40">
+        <v>0.1665702358720827</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -3816,17 +3766,17 @@
       <c r="F41" t="s">
         <v>30</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41">
         <v>38430</v>
       </c>
-      <c r="H41" s="3">
-        <v>37023.937819420833</v>
-      </c>
-      <c r="I41" s="3">
-        <v>-1406.0621805791741</v>
-      </c>
-      <c r="J41" s="5">
-        <v>-3.6587618542263188E-2</v>
+      <c r="H41">
+        <v>37023.93781942083</v>
+      </c>
+      <c r="I41">
+        <v>-1406.062180579174</v>
+      </c>
+      <c r="J41">
+        <v>-0.03658761854226319</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2021_2024_raw.xlsx
+++ b/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2021_2024_raw.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vasilauskas\GitHub-Local\EV-Transition-MI-Mobility\data\processed\sam_auto_dashboard_2024_refresh\occ_change_by_education\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B5579D-1A79-447B-A692-F881B8E15E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
     <sheet name="Education+Training" sheetId="2" r:id="rId2"/>
     <sheet name="Edu+Training (custom)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="34">
   <si>
     <t>methodology</t>
   </si>
@@ -46,6 +52,15 @@
   </si>
   <si>
     <t>pct_change</t>
+  </si>
+  <si>
+    <t>share_base</t>
+  </si>
+  <si>
+    <t>share_target</t>
+  </si>
+  <si>
+    <t>share_change</t>
   </si>
   <si>
     <t>sam_mi_moodys_mi</t>
@@ -90,16 +105,16 @@
     <t>BA+</t>
   </si>
   <si>
+    <t>SC or Associate's</t>
+  </si>
+  <si>
     <t>HS or Less</t>
   </si>
   <si>
-    <t>SC or Associate's</t>
+    <t>SC/Associate or Employer Training</t>
   </si>
   <si>
     <t>HS or Less - Limited Training</t>
-  </si>
-  <si>
-    <t>SC/Associate or Employer Training</t>
   </si>
   <si>
     <t>Associate's</t>
@@ -114,8 +129,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,13 +193,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -222,7 +245,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -256,6 +279,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -290,9 +314,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -465,11 +490,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="15.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,25 +528,34 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>11960</v>
@@ -530,667 +567,856 @@
         <v>-164.5055036924241</v>
       </c>
       <c r="J2">
-        <v>-0.01375464077695854</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>-1.3754640776958539E-2</v>
+      </c>
+      <c r="K2">
+        <v>0.17044320934872451</v>
+      </c>
+      <c r="L2">
+        <v>0.16246342482931489</v>
+      </c>
+      <c r="M2">
+        <v>-6.7586484672318828E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>55220</v>
+        <v>2990</v>
       </c>
       <c r="H3">
-        <v>57389.22836839916</v>
+        <v>3419.27713529327</v>
       </c>
       <c r="I3">
-        <v>2169.228368399155</v>
+        <v>429.27713529326962</v>
       </c>
       <c r="J3">
-        <v>0.03928338226003541</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>0.1435709482586186</v>
+      </c>
+      <c r="K3">
+        <v>4.2610802337181133E-2</v>
+      </c>
+      <c r="L3">
+        <v>4.7094886442803012E-2</v>
+      </c>
+      <c r="M3">
+        <v>0.17636694136946149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>2990</v>
+        <v>55220</v>
       </c>
       <c r="H4">
-        <v>3419.27713529327</v>
+        <v>57389.228368399163</v>
       </c>
       <c r="I4">
-        <v>429.2771352932696</v>
+        <v>2169.228368399155</v>
       </c>
       <c r="J4">
-        <v>0.1435709482586186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>3.9283382260035409E-2</v>
+      </c>
+      <c r="K4">
+        <v>0.78694598831409435</v>
+      </c>
+      <c r="L4">
+        <v>0.79044168872788212</v>
+      </c>
+      <c r="M4">
+        <v>0.89121954330285724</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>11390</v>
       </c>
       <c r="H5">
-        <v>12673.95038167937</v>
+        <v>12673.950381679369</v>
       </c>
       <c r="I5">
-        <v>1283.950381679368</v>
+        <v>1283.9503816793681</v>
       </c>
       <c r="J5">
         <v>0.1127261090148699</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>0.24717881944444439</v>
+      </c>
+      <c r="L5">
+        <v>0.26653944020356191</v>
+      </c>
+      <c r="M5">
+        <v>0.87343563379548872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>28480</v>
+        <v>6210</v>
       </c>
       <c r="H6">
-        <v>29602.79898218832</v>
+        <v>5273.2506361323149</v>
       </c>
       <c r="I6">
-        <v>1122.798982188317</v>
+        <v>-936.74936386768513</v>
       </c>
       <c r="J6">
-        <v>0.039424121565601</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>-0.15084530819125361</v>
+      </c>
+      <c r="K6">
+        <v>0.134765625</v>
+      </c>
+      <c r="L6">
+        <v>0.1108990670059372</v>
+      </c>
+      <c r="M6">
+        <v>-0.63724446521611278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>6210</v>
+        <v>28480</v>
       </c>
       <c r="H7">
-        <v>5273.250636132315</v>
+        <v>29602.79898218832</v>
       </c>
       <c r="I7">
-        <v>-936.7493638676851</v>
+        <v>1122.798982188317</v>
       </c>
       <c r="J7">
-        <v>-0.1508453081912536</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>3.9424121565601003E-2</v>
+      </c>
+      <c r="K7">
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="L7">
+        <v>0.62256149279050088</v>
+      </c>
+      <c r="M7">
+        <v>0.76380883142062395</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>1800</v>
       </c>
       <c r="H8">
-        <v>2072.910804020093</v>
+        <v>2072.9108040200931</v>
       </c>
       <c r="I8">
-        <v>272.9108040200927</v>
+        <v>272.91080402009271</v>
       </c>
       <c r="J8">
         <v>0.1516171133444959</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>0.1282965074839629</v>
+      </c>
+      <c r="L8">
+        <v>0.12688442211055229</v>
+      </c>
+      <c r="M8">
+        <v>0.11829683745994481</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>11440</v>
+        <v>790</v>
       </c>
       <c r="H9">
-        <v>13525.2298994975</v>
+        <v>738.85929648241051</v>
       </c>
       <c r="I9">
-        <v>2085.229899497497</v>
+        <v>-51.140703517589493</v>
       </c>
       <c r="J9">
-        <v>0.1822753408651658</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>-6.4735067743784167E-2</v>
+      </c>
+      <c r="K9">
+        <v>5.6307911617961511E-2</v>
+      </c>
+      <c r="L9">
+        <v>4.5226130653266243E-2</v>
+      </c>
+      <c r="M9">
+        <v>-2.2167621810832022E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G10">
-        <v>790</v>
+        <v>11440</v>
       </c>
       <c r="H10">
-        <v>738.8592964824105</v>
+        <v>13525.229899497501</v>
       </c>
       <c r="I10">
-        <v>-51.14070351758949</v>
+        <v>2085.2298994974972</v>
       </c>
       <c r="J10">
-        <v>-0.06473506774378417</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.18227534086516581</v>
+      </c>
+      <c r="K10">
+        <v>0.81539558089807551</v>
+      </c>
+      <c r="L10">
+        <v>0.82788944723618152</v>
+      </c>
+      <c r="M10">
+        <v>0.90387078435088719</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G11">
         <v>7700</v>
       </c>
       <c r="H11">
-        <v>8607.45361224091</v>
+        <v>8607.4536122409099</v>
       </c>
       <c r="I11">
-        <v>907.4536122409099</v>
+        <v>907.45361224090993</v>
       </c>
       <c r="J11">
-        <v>0.1178511184728454</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>0.11785111847284541</v>
+      </c>
+      <c r="K11">
+        <v>0.16882262661697001</v>
+      </c>
+      <c r="L11">
+        <v>0.17063722641874809</v>
+      </c>
+      <c r="M11">
+        <v>0.1877619723237966</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G12">
-        <v>35530</v>
+        <v>2380</v>
       </c>
       <c r="H12">
-        <v>39178.08057331014</v>
+        <v>2657.4658144489508</v>
       </c>
       <c r="I12">
-        <v>3648.080573310144</v>
+        <v>277.46581444895128</v>
       </c>
       <c r="J12">
-        <v>0.1026760645457401</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>0.116582274978551</v>
+      </c>
+      <c r="K12">
+        <v>5.2181539136154351E-2</v>
+      </c>
+      <c r="L12">
+        <v>5.2682548905674739E-2</v>
+      </c>
+      <c r="M12">
+        <v>5.7410679588030408E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G13">
-        <v>2380</v>
+        <v>35530</v>
       </c>
       <c r="H13">
-        <v>2657.465814448951</v>
+        <v>39178.080573310137</v>
       </c>
       <c r="I13">
-        <v>277.4658144489513</v>
+        <v>3648.0805733101438</v>
       </c>
       <c r="J13">
-        <v>0.116582274978551</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>0.1026760645457401</v>
+      </c>
+      <c r="K13">
+        <v>0.77899583424687568</v>
+      </c>
+      <c r="L13">
+        <v>0.77668022467557718</v>
+      </c>
+      <c r="M13">
+        <v>0.75482734808817298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G14">
         <v>4810</v>
       </c>
       <c r="H14">
-        <v>7463.377722464218</v>
+        <v>7463.3777224642181</v>
       </c>
       <c r="I14">
-        <v>2653.377722464218</v>
+        <v>2653.3777224642181</v>
       </c>
       <c r="J14">
-        <v>0.5516377801380911</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>0.55163778013809106</v>
+      </c>
+      <c r="K14">
+        <v>0.32654446707399859</v>
+      </c>
+      <c r="L14">
+        <v>0.4082140634723086</v>
+      </c>
+      <c r="M14">
+        <v>0.74679924640141249</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G15">
-        <v>9360</v>
+        <v>560</v>
       </c>
       <c r="H15">
-        <v>9772.929060360926</v>
+        <v>1046.6932171748549</v>
       </c>
       <c r="I15">
-        <v>412.9290603609261</v>
+        <v>486.69321717485542</v>
       </c>
       <c r="J15">
-        <v>0.04411635260266304</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>0.86909503066938454</v>
+      </c>
+      <c r="K15">
+        <v>3.8017651052274268E-2</v>
+      </c>
+      <c r="L15">
+        <v>5.7249533291847912E-2</v>
+      </c>
+      <c r="M15">
+        <v>0.13698092236838039</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G16">
-        <v>560</v>
+        <v>9360</v>
       </c>
       <c r="H16">
-        <v>1046.693217174855</v>
+        <v>9772.9290603609261</v>
       </c>
       <c r="I16">
-        <v>486.6932171748554</v>
+        <v>412.92906036092609</v>
       </c>
       <c r="J16">
-        <v>0.8690950306693845</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>4.4116352602663042E-2</v>
+      </c>
+      <c r="K16">
+        <v>0.63543788187372707</v>
+      </c>
+      <c r="L16">
+        <v>0.5345364032358435</v>
+      </c>
+      <c r="M16">
+        <v>0.1162198312302072</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>83510</v>
       </c>
       <c r="H17">
-        <v>85951.42274573538</v>
+        <v>85951.422745735385</v>
       </c>
       <c r="I17">
         <v>2441.422745735385</v>
       </c>
       <c r="J17">
-        <v>0.02923509454838204</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>2.9235094548382041E-2</v>
+      </c>
+      <c r="K17">
+        <v>0.72165572070515038</v>
+      </c>
+      <c r="L17">
+        <v>0.71502843216896994</v>
+      </c>
+      <c r="M17">
+        <v>0.5441102620315087</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G18">
-        <v>19910</v>
+        <v>12300</v>
       </c>
       <c r="H18">
-        <v>23289.49593826145</v>
+        <v>10966.08131600317</v>
       </c>
       <c r="I18">
-        <v>3379.495938261454</v>
+        <v>-1333.9186839968299</v>
       </c>
       <c r="J18">
-        <v>0.1697386207062508</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>-0.1084486734956772</v>
+      </c>
+      <c r="K18">
+        <v>0.10629104735568611</v>
+      </c>
+      <c r="L18">
+        <v>9.1226645004061066E-2</v>
+      </c>
+      <c r="M18">
+        <v>-0.29728519812721799</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G19">
-        <v>12300</v>
+        <v>19910</v>
       </c>
       <c r="H19">
-        <v>10966.08131600317</v>
+        <v>23289.495938261451</v>
       </c>
       <c r="I19">
-        <v>-1333.91868399683</v>
+        <v>3379.4959382614538</v>
       </c>
       <c r="J19">
-        <v>-0.1084486734956772</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>0.16973862070625079</v>
+      </c>
+      <c r="K19">
+        <v>0.1720532319391635</v>
+      </c>
+      <c r="L19">
+        <v>0.1937449228269689</v>
+      </c>
+      <c r="M19">
+        <v>0.75317493609570929</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G20">
         <v>24380</v>
       </c>
       <c r="H20">
-        <v>28420.73848797222</v>
+        <v>28420.738487972219</v>
       </c>
       <c r="I20">
         <v>4040.738487972219</v>
       </c>
       <c r="J20">
-        <v>0.1657398887601403</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>0.16573988876014031</v>
+      </c>
+      <c r="K20">
+        <v>0.1449809705042816</v>
+      </c>
+      <c r="L20">
+        <v>0.16420389461626411</v>
+      </c>
+      <c r="M20">
+        <v>0.82095458918573783</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21">
-        <v>135650</v>
+        <v>8130</v>
       </c>
       <c r="H21">
-        <v>136344.2054982822</v>
+        <v>8317.0560137456159</v>
       </c>
       <c r="I21">
-        <v>694.2054982821865</v>
+        <v>187.0560137456159</v>
       </c>
       <c r="J21">
-        <v>0.005117622545390243</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>2.3008119771908479E-2</v>
+      </c>
+      <c r="K21">
+        <v>4.8346812559467177E-2</v>
+      </c>
+      <c r="L21">
+        <v>4.8052691867124353E-2</v>
+      </c>
+      <c r="M21">
+        <v>3.8004066181555281E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G22">
-        <v>8130</v>
+        <v>135650</v>
       </c>
       <c r="H22">
-        <v>8317.056013745616</v>
+        <v>136344.20549828219</v>
       </c>
       <c r="I22">
-        <v>187.0560137456159</v>
+        <v>694.20549828218645</v>
       </c>
       <c r="J22">
-        <v>0.02300811977190848</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>5.117622545390243E-3</v>
+      </c>
+      <c r="K22">
+        <v>0.80667221693625124</v>
+      </c>
+      <c r="L22">
+        <v>0.7877434135166117</v>
+      </c>
+      <c r="M22">
+        <v>0.1410413446327069</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G23">
         <v>15400</v>
@@ -1199,266 +1425,347 @@
         <v>19646.96893063571</v>
       </c>
       <c r="I23">
-        <v>4246.968930635714</v>
+        <v>4246.9689306357141</v>
       </c>
       <c r="J23">
         <v>0.2757772032880334</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23">
+        <v>0.15305108328364139</v>
+      </c>
+      <c r="L23">
+        <v>0.17033959537572149</v>
+      </c>
+      <c r="M23">
+        <v>0.28851691104862182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G24">
-        <v>77320</v>
+        <v>7900</v>
       </c>
       <c r="H24">
-        <v>87775.90679190768</v>
+        <v>7917.1242774566126</v>
       </c>
       <c r="I24">
-        <v>10455.90679190768</v>
+        <v>17.124277456612621</v>
       </c>
       <c r="J24">
-        <v>0.1352290066206373</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>2.1676300577990648E-3</v>
+      </c>
+      <c r="K24">
+        <v>7.8513218048101768E-2</v>
+      </c>
+      <c r="L24">
+        <v>6.8641618497109522E-2</v>
+      </c>
+      <c r="M24">
+        <v>1.1633340663459661E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G25">
-        <v>7900</v>
+        <v>77320</v>
       </c>
       <c r="H25">
-        <v>7917.124277456613</v>
+        <v>87775.906791907677</v>
       </c>
       <c r="I25">
-        <v>17.12427745661262</v>
+        <v>10455.906791907681</v>
       </c>
       <c r="J25">
-        <v>0.002167630057799065</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>0.1352290066206373</v>
+      </c>
+      <c r="K25">
+        <v>0.76843569866825678</v>
+      </c>
+      <c r="L25">
+        <v>0.761018786127169</v>
+      </c>
+      <c r="M25">
+        <v>0.71031975488503218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G26">
         <v>4600</v>
       </c>
       <c r="H26">
-        <v>6147.44206383908</v>
+        <v>6147.4420638390802</v>
       </c>
       <c r="I26">
         <v>1547.44206383908</v>
       </c>
       <c r="J26">
-        <v>0.3364004486606696</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>0.33640044866066959</v>
+      </c>
+      <c r="K26">
+        <v>7.1362085013962143E-2</v>
+      </c>
+      <c r="L26">
+        <v>8.8325317009182183E-2</v>
+      </c>
+      <c r="M26">
+        <v>0.30105876728386749</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G27">
-        <v>43860</v>
+        <v>16000</v>
       </c>
       <c r="H27">
-        <v>45578.31219938782</v>
+        <v>17874.245736773111</v>
       </c>
       <c r="I27">
-        <v>1718.312199387816</v>
+        <v>1874.2457367731081</v>
       </c>
       <c r="J27">
-        <v>0.03917720472840437</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>0.1171403585483192</v>
+      </c>
+      <c r="K27">
+        <v>0.24821594787465101</v>
+      </c>
+      <c r="L27">
+        <v>0.25681387552834922</v>
+      </c>
+      <c r="M27">
+        <v>0.36463924839943701</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G28">
-        <v>16000</v>
+        <v>43860</v>
       </c>
       <c r="H28">
-        <v>17874.24573677311</v>
+        <v>45578.312199387823</v>
       </c>
       <c r="I28">
-        <v>1874.245736773108</v>
+        <v>1718.312199387816</v>
       </c>
       <c r="J28">
-        <v>0.1171403585483192</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>3.9177204728404372E-2</v>
+      </c>
+      <c r="K28">
+        <v>0.68042196711138692</v>
+      </c>
+      <c r="L28">
+        <v>0.65486080746246866</v>
+      </c>
+      <c r="M28">
+        <v>0.33430198431669539</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G29">
         <v>1650</v>
       </c>
       <c r="H29">
-        <v>3914.073253833027</v>
+        <v>3914.0732538330271</v>
       </c>
       <c r="I29">
-        <v>2264.073253833027</v>
+        <v>2264.0732538330271</v>
       </c>
       <c r="J29">
-        <v>1.372165608383653</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>1.3721656083836531</v>
+      </c>
+      <c r="K29">
+        <v>3.6609718216108277E-2</v>
+      </c>
+      <c r="L29">
+        <v>8.347529812606426E-2</v>
+      </c>
+      <c r="M29">
+        <v>1.2446801835255761</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G30">
-        <v>14360</v>
+        <v>29060</v>
       </c>
       <c r="H30">
-        <v>15786.09646507664</v>
+        <v>27188.830281090341</v>
       </c>
       <c r="I30">
-        <v>1426.096465076636</v>
+        <v>-1871.169718909659</v>
       </c>
       <c r="J30">
-        <v>0.09931033879363763</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>-6.4389873327930475E-2</v>
+      </c>
+      <c r="K30">
+        <v>0.64477479476370092</v>
+      </c>
+      <c r="L30">
+        <v>0.5798551959114151</v>
+      </c>
+      <c r="M30">
+        <v>-1.0286804392026689</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G31">
-        <v>29060</v>
+        <v>14360</v>
       </c>
       <c r="H31">
-        <v>27188.83028109034</v>
+        <v>15786.09646507664</v>
       </c>
       <c r="I31">
-        <v>-1871.169718909659</v>
+        <v>1426.0964650766359</v>
       </c>
       <c r="J31">
-        <v>-0.06438987332793047</v>
+        <v>9.9310338793637626E-2</v>
+      </c>
+      <c r="K31">
+        <v>0.31861548702019082</v>
+      </c>
+      <c r="L31">
+        <v>0.33666950596252082</v>
+      </c>
+      <c r="M31">
+        <v>0.78400025567709353</v>
       </c>
     </row>
   </sheetData>
@@ -1467,11 +1774,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1502,25 +1809,34 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>11960</v>
@@ -1532,667 +1848,856 @@
         <v>-164.5055036924241</v>
       </c>
       <c r="J2">
-        <v>-0.01375464077695854</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>-1.3754640776958539E-2</v>
+      </c>
+      <c r="K2">
+        <v>0.17044320934872451</v>
+      </c>
+      <c r="L2">
+        <v>0.16246342482931489</v>
+      </c>
+      <c r="M2">
+        <v>-6.7586484672318814E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>14780</v>
+        <v>43430</v>
       </c>
       <c r="H3">
-        <v>15083.26097255121</v>
+        <v>45725.244531141223</v>
       </c>
       <c r="I3">
-        <v>303.2609725512102</v>
+        <v>2295.2445311412162</v>
       </c>
       <c r="J3">
-        <v>0.02051833373147566</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>5.2849286924734423E-2</v>
+      </c>
+      <c r="K3">
+        <v>0.6189254667236711</v>
+      </c>
+      <c r="L3">
+        <v>0.62978960568482745</v>
+      </c>
+      <c r="M3">
+        <v>0.94299282298324316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>43430</v>
+        <v>14780</v>
       </c>
       <c r="H4">
-        <v>45725.24453114122</v>
+        <v>15083.26097255121</v>
       </c>
       <c r="I4">
-        <v>2295.244531141216</v>
+        <v>303.26097255121022</v>
       </c>
       <c r="J4">
-        <v>0.05284928692473442</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>2.0518333731475661E-2</v>
+      </c>
+      <c r="K4">
+        <v>0.21063132392760439</v>
+      </c>
+      <c r="L4">
+        <v>0.20774696948585769</v>
+      </c>
+      <c r="M4">
+        <v>0.1245936616890756</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>11390</v>
       </c>
       <c r="H5">
-        <v>12673.95038167937</v>
+        <v>12673.950381679369</v>
       </c>
       <c r="I5">
-        <v>1283.950381679368</v>
+        <v>1283.9503816793681</v>
       </c>
       <c r="J5">
         <v>0.1127261090148699</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>0.24717881944444439</v>
+      </c>
+      <c r="L5">
+        <v>0.26653944020356191</v>
+      </c>
+      <c r="M5">
+        <v>0.87343563379548927</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>6460</v>
+        <v>28230</v>
       </c>
       <c r="H6">
-        <v>6513.422391857504</v>
+        <v>28362.62722646313</v>
       </c>
       <c r="I6">
-        <v>53.42239185750441</v>
+        <v>132.62722646312611</v>
       </c>
       <c r="J6">
-        <v>0.008269720101780868</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>4.6980951634121903E-3</v>
+      </c>
+      <c r="K6">
+        <v>0.61263020833333337</v>
+      </c>
+      <c r="L6">
+        <v>0.59648006785411412</v>
+      </c>
+      <c r="M6">
+        <v>9.0222603036140339E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>28230</v>
+        <v>6460</v>
       </c>
       <c r="H7">
-        <v>28362.62722646313</v>
+        <v>6513.4223918575044</v>
       </c>
       <c r="I7">
-        <v>132.6272264631261</v>
+        <v>53.422391857504408</v>
       </c>
       <c r="J7">
-        <v>0.00469809516341219</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>8.269720101780868E-3</v>
+      </c>
+      <c r="K7">
+        <v>0.14019097222222221</v>
+      </c>
+      <c r="L7">
+        <v>0.13698049194232401</v>
+      </c>
+      <c r="M7">
+        <v>3.6341763168370393E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>1800</v>
       </c>
       <c r="H8">
-        <v>2072.910804020093</v>
+        <v>2072.9108040200931</v>
       </c>
       <c r="I8">
-        <v>272.9108040200927</v>
+        <v>272.91080402009271</v>
       </c>
       <c r="J8">
         <v>0.1516171133444959</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>0.1282965074839629</v>
+      </c>
+      <c r="L8">
+        <v>0.12688442211055229</v>
+      </c>
+      <c r="M8">
+        <v>0.11829683745994481</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G9">
-        <v>2350</v>
+        <v>9880</v>
       </c>
       <c r="H9">
-        <v>2883.60364321608</v>
+        <v>11380.48555276383</v>
       </c>
       <c r="I9">
-        <v>533.6036432160804</v>
+        <v>1500.485552763826</v>
       </c>
       <c r="J9">
-        <v>0.2270653800919491</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>0.15187100736475981</v>
+      </c>
+      <c r="K9">
+        <v>0.70420527441197434</v>
+      </c>
+      <c r="L9">
+        <v>0.69660804020100553</v>
+      </c>
+      <c r="M9">
+        <v>0.65040552785601513</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G10">
-        <v>9880</v>
+        <v>2350</v>
       </c>
       <c r="H10">
-        <v>11380.48555276383</v>
+        <v>2883.6036432160799</v>
       </c>
       <c r="I10">
-        <v>1500.485552763826</v>
+        <v>533.6036432160804</v>
       </c>
       <c r="J10">
-        <v>0.1518710073647598</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.2270653800919491</v>
+      </c>
+      <c r="K10">
+        <v>0.16749821810406271</v>
+      </c>
+      <c r="L10">
+        <v>0.17650753768844221</v>
+      </c>
+      <c r="M10">
+        <v>0.2312976346840401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G11">
         <v>7700</v>
       </c>
       <c r="H11">
-        <v>8607.45361224091</v>
+        <v>8607.4536122409099</v>
       </c>
       <c r="I11">
-        <v>907.4536122409099</v>
+        <v>907.45361224090993</v>
       </c>
       <c r="J11">
-        <v>0.1178511184728454</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>0.11785111847284541</v>
+      </c>
+      <c r="K11">
+        <v>0.16882262661697001</v>
+      </c>
+      <c r="L11">
+        <v>0.17063722641874809</v>
+      </c>
+      <c r="M11">
+        <v>0.18776197232379671</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G12">
-        <v>7880</v>
+        <v>30030</v>
       </c>
       <c r="H12">
-        <v>8001.707728065074</v>
+        <v>33833.838659694018</v>
       </c>
       <c r="I12">
-        <v>121.7077280650738</v>
+        <v>3803.8386596940181</v>
       </c>
       <c r="J12">
-        <v>0.01544514315546621</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>0.12666795403576481</v>
+      </c>
+      <c r="K12">
+        <v>0.6584082438061829</v>
+      </c>
+      <c r="L12">
+        <v>0.67073406933953206</v>
+      </c>
+      <c r="M12">
+        <v>0.78705538168715428</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G13">
-        <v>30030</v>
+        <v>7880</v>
       </c>
       <c r="H13">
-        <v>33833.83865969402</v>
+        <v>8001.7077280650738</v>
       </c>
       <c r="I13">
-        <v>3803.838659694018</v>
+        <v>121.70772806507379</v>
       </c>
       <c r="J13">
-        <v>0.1266679540357648</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>1.5445143155466211E-2</v>
+      </c>
+      <c r="K13">
+        <v>0.1727691295768472</v>
+      </c>
+      <c r="L13">
+        <v>0.15862870424171979</v>
+      </c>
+      <c r="M13">
+        <v>2.5182645989048982E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G14">
         <v>4810</v>
       </c>
       <c r="H14">
-        <v>7463.377722464218</v>
+        <v>7463.3777224642181</v>
       </c>
       <c r="I14">
-        <v>2653.377722464218</v>
+        <v>2653.3777224642181</v>
       </c>
       <c r="J14">
-        <v>0.5516377801380911</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>0.55163778013809106</v>
+      </c>
+      <c r="K14">
+        <v>0.32654446707399859</v>
+      </c>
+      <c r="L14">
+        <v>0.4082140634723086</v>
+      </c>
+      <c r="M14">
+        <v>0.74679924640141271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G15">
-        <v>2300</v>
+        <v>7620</v>
       </c>
       <c r="H15">
-        <v>2355.059738643429</v>
+        <v>8464.5625388923509</v>
       </c>
       <c r="I15">
-        <v>55.05973864342923</v>
+        <v>844.56253889235086</v>
       </c>
       <c r="J15">
-        <v>0.02393901680149097</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>0.1108349788572639</v>
+      </c>
+      <c r="K15">
+        <v>0.51731160896130346</v>
+      </c>
+      <c r="L15">
+        <v>0.46297448662103319</v>
+      </c>
+      <c r="M15">
+        <v>0.23770406385937271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G16">
-        <v>7620</v>
+        <v>2300</v>
       </c>
       <c r="H16">
-        <v>8464.562538892351</v>
+        <v>2355.0597386434288</v>
       </c>
       <c r="I16">
-        <v>844.5625388923509</v>
+        <v>55.059738643429228</v>
       </c>
       <c r="J16">
-        <v>0.1108349788572639</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>2.3939016801490971E-2</v>
+      </c>
+      <c r="K16">
+        <v>0.15614392396469789</v>
+      </c>
+      <c r="L16">
+        <v>0.12881144990665799</v>
+      </c>
+      <c r="M16">
+        <v>1.549668973921454E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>83510</v>
       </c>
       <c r="H17">
-        <v>85951.42274573538</v>
+        <v>85951.422745735385</v>
       </c>
       <c r="I17">
         <v>2441.422745735385</v>
       </c>
       <c r="J17">
-        <v>0.02923509454838204</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>2.9235094548382041E-2</v>
+      </c>
+      <c r="K17">
+        <v>0.72165572070515038</v>
+      </c>
+      <c r="L17">
+        <v>0.71502843216896994</v>
+      </c>
+      <c r="M17">
+        <v>0.54411026203150847</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>7230</v>
+        <v>24980</v>
       </c>
       <c r="H18">
-        <v>8964.258813972308</v>
+        <v>25291.318440292322</v>
       </c>
       <c r="I18">
-        <v>1734.258813972308</v>
+        <v>311.31844029231797</v>
       </c>
       <c r="J18">
-        <v>0.2398698221261837</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>1.246270777791505E-2</v>
+      </c>
+      <c r="K18">
+        <v>0.2158658831662634</v>
+      </c>
+      <c r="L18">
+        <v>0.21039805036555539</v>
+      </c>
+      <c r="M18">
+        <v>6.9382313414824426E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G19">
-        <v>24980</v>
+        <v>7230</v>
       </c>
       <c r="H19">
-        <v>25291.31844029232</v>
+        <v>8964.2588139723084</v>
       </c>
       <c r="I19">
-        <v>311.318440292318</v>
+        <v>1734.258813972308</v>
       </c>
       <c r="J19">
-        <v>0.01246270777791505</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>0.23986982212618371</v>
+      </c>
+      <c r="K19">
+        <v>6.2478396128586237E-2</v>
+      </c>
+      <c r="L19">
+        <v>7.4573517465474623E-2</v>
+      </c>
+      <c r="M19">
+        <v>0.3865074245536671</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G20">
         <v>24380</v>
       </c>
       <c r="H20">
-        <v>28420.73848797222</v>
+        <v>28420.738487972219</v>
       </c>
       <c r="I20">
         <v>4040.738487972219</v>
       </c>
       <c r="J20">
-        <v>0.1657398887601403</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>0.16573988876014031</v>
+      </c>
+      <c r="K20">
+        <v>0.1449809705042816</v>
+      </c>
+      <c r="L20">
+        <v>0.16420389461626411</v>
+      </c>
+      <c r="M20">
+        <v>0.82095458918574082</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G21">
-        <v>18310</v>
+        <v>125470</v>
       </c>
       <c r="H21">
-        <v>19251.15945017174</v>
+        <v>125410.102061856</v>
       </c>
       <c r="I21">
-        <v>941.1594501717409</v>
+        <v>-59.897938143956708</v>
       </c>
       <c r="J21">
-        <v>0.05140138996022615</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>-4.7738852430028459E-4</v>
+      </c>
+      <c r="K21">
+        <v>0.74613463368220745</v>
+      </c>
+      <c r="L21">
+        <v>0.72457044673539739</v>
+      </c>
+      <c r="M21">
+        <v>-1.2169430748467431E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G22">
-        <v>125470</v>
+        <v>18310</v>
       </c>
       <c r="H22">
-        <v>125410.102061856</v>
+        <v>19251.159450171741</v>
       </c>
       <c r="I22">
-        <v>-59.89793814395671</v>
+        <v>941.1594501717409</v>
       </c>
       <c r="J22">
-        <v>-0.0004773885243002846</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>5.1401389960226147E-2</v>
+      </c>
+      <c r="K22">
+        <v>0.10888439581351091</v>
+      </c>
+      <c r="L22">
+        <v>0.1112256586483386</v>
+      </c>
+      <c r="M22">
+        <v>0.19121484156272661</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G23">
         <v>15400</v>
@@ -2201,266 +2706,347 @@
         <v>19646.96893063571</v>
       </c>
       <c r="I23">
-        <v>4246.968930635714</v>
+        <v>4246.9689306357141</v>
       </c>
       <c r="J23">
         <v>0.2757772032880334</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23">
+        <v>0.15305108328364139</v>
+      </c>
+      <c r="L23">
+        <v>0.17033959537572141</v>
+      </c>
+      <c r="M23">
+        <v>0.28851691104862159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G24">
-        <v>51050</v>
+        <v>34170</v>
       </c>
       <c r="H24">
-        <v>60774.34609826608</v>
+        <v>34918.684971098213</v>
       </c>
       <c r="I24">
-        <v>9724.346098266084</v>
+        <v>748.68497109821328</v>
       </c>
       <c r="J24">
-        <v>0.1904867012392965</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>2.1910593242558191E-2</v>
+      </c>
+      <c r="K24">
+        <v>0.33959451401311869</v>
+      </c>
+      <c r="L24">
+        <v>0.3027456647398839</v>
+      </c>
+      <c r="M24">
+        <v>5.0861750753954667E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G25">
-        <v>34170</v>
+        <v>51050</v>
       </c>
       <c r="H25">
-        <v>34918.68497109821</v>
+        <v>60774.346098266084</v>
       </c>
       <c r="I25">
-        <v>748.6849710982133</v>
+        <v>9724.3460982660836</v>
       </c>
       <c r="J25">
-        <v>0.02191059324255819</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>0.19048670123929651</v>
+      </c>
+      <c r="K25">
+        <v>0.50735440270323995</v>
+      </c>
+      <c r="L25">
+        <v>0.52691473988439463</v>
+      </c>
+      <c r="M25">
+        <v>0.66062133819742364</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G26">
         <v>4600</v>
       </c>
       <c r="H26">
-        <v>6147.44206383908</v>
+        <v>6147.4420638390802</v>
       </c>
       <c r="I26">
         <v>1547.44206383908</v>
       </c>
       <c r="J26">
-        <v>0.3364004486606696</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>0.33640044866066959</v>
+      </c>
+      <c r="K26">
+        <v>7.1362085013962143E-2</v>
+      </c>
+      <c r="L26">
+        <v>8.8325317009182183E-2</v>
+      </c>
+      <c r="M26">
+        <v>0.30105876728386782</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G27">
-        <v>34400</v>
+        <v>25460</v>
       </c>
       <c r="H27">
-        <v>34734.06209007435</v>
+        <v>28718.495846086571</v>
       </c>
       <c r="I27">
-        <v>334.0620900743525</v>
+        <v>3258.4958460865669</v>
       </c>
       <c r="J27">
-        <v>0.009711107269603269</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>0.12798491147237109</v>
+      </c>
+      <c r="K27">
+        <v>0.39497362705553829</v>
+      </c>
+      <c r="L27">
+        <v>0.41262206675411728</v>
+      </c>
+      <c r="M27">
+        <v>0.6339486081880481</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G28">
-        <v>25460</v>
+        <v>34400</v>
       </c>
       <c r="H28">
-        <v>28718.49584608657</v>
+        <v>34734.062090074352</v>
       </c>
       <c r="I28">
-        <v>3258.495846086567</v>
+        <v>334.06209007435251</v>
       </c>
       <c r="J28">
-        <v>0.1279849114723711</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>9.7111072696032686E-3</v>
+      </c>
+      <c r="K28">
+        <v>0.53366428793049958</v>
+      </c>
+      <c r="L28">
+        <v>0.49905261623670039</v>
+      </c>
+      <c r="M28">
+        <v>6.4992624528084131E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G29">
         <v>1650</v>
       </c>
       <c r="H29">
-        <v>3914.073253833027</v>
+        <v>3914.0732538330271</v>
       </c>
       <c r="I29">
-        <v>2264.073253833027</v>
+        <v>2264.0732538330271</v>
       </c>
       <c r="J29">
-        <v>1.372165608383653</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>1.3721656083836531</v>
+      </c>
+      <c r="K29">
+        <v>3.6609718216108277E-2</v>
+      </c>
+      <c r="L29">
+        <v>8.347529812606426E-2</v>
+      </c>
+      <c r="M29">
+        <v>1.2446801835255761</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G30">
-        <v>9880</v>
+        <v>33540</v>
       </c>
       <c r="H30">
-        <v>10643.88287904598</v>
+        <v>32331.043867120999</v>
       </c>
       <c r="I30">
-        <v>763.8828790459811</v>
+        <v>-1208.9561328790039</v>
       </c>
       <c r="J30">
-        <v>0.07731608087509931</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>-3.6045203723285762E-2</v>
+      </c>
+      <c r="K30">
+        <v>0.74417572664743736</v>
+      </c>
+      <c r="L30">
+        <v>0.68952299829642338</v>
+      </c>
+      <c r="M30">
+        <v>-0.66462679102748845</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G31">
-        <v>33540</v>
+        <v>9880</v>
       </c>
       <c r="H31">
-        <v>32331.043867121</v>
+        <v>10643.882879045979</v>
       </c>
       <c r="I31">
-        <v>-1208.956132879004</v>
+        <v>763.8828790459811</v>
       </c>
       <c r="J31">
-        <v>-0.03604520372328576</v>
+        <v>7.7316080875099308E-2</v>
+      </c>
+      <c r="K31">
+        <v>0.21921455513645441</v>
+      </c>
+      <c r="L31">
+        <v>0.22700170357751251</v>
+      </c>
+      <c r="M31">
+        <v>0.41994660750191282</v>
       </c>
     </row>
   </sheetData>
@@ -2469,11 +3055,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:M41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2504,217 +3090,280 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>920</v>
+        <v>11960</v>
       </c>
       <c r="H2">
-        <v>1224.060749616819</v>
+        <v>11795.49449630758</v>
       </c>
       <c r="I2">
-        <v>304.0607496168191</v>
+        <v>-164.5055036924241</v>
       </c>
       <c r="J2">
-        <v>0.3305008148008903</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>-1.3754640776958539E-2</v>
+      </c>
+      <c r="K2">
+        <v>0.17044320934872451</v>
+      </c>
+      <c r="L2">
+        <v>0.16246342482931489</v>
+      </c>
+      <c r="M2">
+        <v>-6.7586484672318717E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>11960</v>
+        <v>920</v>
       </c>
       <c r="H3">
-        <v>11795.49449630758</v>
+        <v>1224.0607496168191</v>
       </c>
       <c r="I3">
-        <v>-164.5055036924241</v>
+        <v>304.06074961681912</v>
       </c>
       <c r="J3">
-        <v>-0.01375464077695854</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>0.33050081480089027</v>
+      </c>
+      <c r="K3">
+        <v>1.3111016103748039E-2</v>
+      </c>
+      <c r="L3">
+        <v>1.6859412010589211E-2</v>
+      </c>
+      <c r="M3">
+        <v>0.12492224717207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>41910</v>
       </c>
       <c r="H4">
-        <v>43782.93325902197</v>
+        <v>43782.933259021971</v>
       </c>
       <c r="I4">
         <v>1872.933259021971</v>
       </c>
       <c r="J4">
-        <v>0.04468941205015441</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>4.4689412050154413E-2</v>
+      </c>
+      <c r="K4">
+        <v>0.5972637879435656</v>
+      </c>
+      <c r="L4">
+        <v>0.6030374808415786</v>
+      </c>
+      <c r="M4">
+        <v>0.76948778102792403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>15380</v>
       </c>
       <c r="H5">
-        <v>15801.51149505364</v>
+        <v>15801.511495053641</v>
       </c>
       <c r="I5">
-        <v>421.511495053639</v>
+        <v>421.51149505363901</v>
       </c>
       <c r="J5">
-        <v>0.0274064691192223</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>2.7406469119222301E-2</v>
+      </c>
+      <c r="K5">
+        <v>0.21918198660396179</v>
+      </c>
+      <c r="L5">
+        <v>0.21763968231851741</v>
+      </c>
+      <c r="M5">
+        <v>0.1731764564723246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>670</v>
+        <v>11390</v>
       </c>
       <c r="H6">
-        <v>836.8638676844718</v>
+        <v>12673.950381679369</v>
       </c>
       <c r="I6">
-        <v>166.8638676844718</v>
+        <v>1283.9503816793681</v>
       </c>
       <c r="J6">
-        <v>0.2490505487827937</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>0.1127261090148699</v>
+      </c>
+      <c r="K6">
+        <v>0.24717881944444439</v>
+      </c>
+      <c r="L6">
+        <v>0.26653944020356191</v>
+      </c>
+      <c r="M6">
+        <v>0.8734356337954885</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>11390</v>
+        <v>670</v>
       </c>
       <c r="H7">
-        <v>12673.95038167937</v>
+        <v>836.86386768447176</v>
       </c>
       <c r="I7">
-        <v>1283.950381679368</v>
+        <v>166.86386768447181</v>
       </c>
       <c r="J7">
-        <v>0.1127261090148699</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>0.2490505487827937</v>
+      </c>
+      <c r="K7">
+        <v>1.4539930555555559E-2</v>
+      </c>
+      <c r="L7">
+        <v>1.7599660729431581E-2</v>
+      </c>
+      <c r="M7">
+        <v>0.1135128351595046</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>27150</v>
@@ -2726,513 +3375,657 @@
         <v>133.7786259542336</v>
       </c>
       <c r="J8">
-        <v>0.004927389537909155</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>4.9273895379091546E-3</v>
+      </c>
+      <c r="K8">
+        <v>0.58919270833333337</v>
+      </c>
+      <c r="L8">
+        <v>0.57379134860050962</v>
+      </c>
+      <c r="M8">
+        <v>9.1005867996077294E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G9">
         <v>6870</v>
       </c>
       <c r="H9">
-        <v>6755.407124681927</v>
+        <v>6755.4071246819267</v>
       </c>
       <c r="I9">
         <v>-114.5928753180733</v>
       </c>
       <c r="J9">
-        <v>-0.01668018563581853</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>-1.668018563581853E-2</v>
+      </c>
+      <c r="K9">
+        <v>0.14908854166666671</v>
+      </c>
+      <c r="L9">
+        <v>0.14206955046649691</v>
+      </c>
+      <c r="M9">
+        <v>-7.7954336951070305E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10">
-        <v>50</v>
+        <v>1800</v>
       </c>
       <c r="H10">
-        <v>123.1432160804015</v>
+        <v>2072.9108040200931</v>
       </c>
       <c r="I10">
-        <v>73.14321608040147</v>
+        <v>272.91080402009271</v>
       </c>
       <c r="J10">
-        <v>1.462864321608029</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.1516171133444959</v>
+      </c>
+      <c r="K10">
+        <v>0.1282965074839629</v>
+      </c>
+      <c r="L10">
+        <v>0.12688442211055229</v>
+      </c>
+      <c r="M10">
+        <v>0.11829683745994481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G11">
-        <v>1800</v>
+        <v>50</v>
       </c>
       <c r="H11">
-        <v>2072.910804020093</v>
+        <v>123.1432160804015</v>
       </c>
       <c r="I11">
-        <v>272.9108040200927</v>
+        <v>73.143216080401473</v>
       </c>
       <c r="J11">
-        <v>0.1516171133444959</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>1.462864321608029</v>
+      </c>
+      <c r="K11">
+        <v>3.5637918745545262E-3</v>
+      </c>
+      <c r="L11">
+        <v>7.5376884422110211E-3</v>
+      </c>
+      <c r="M11">
+        <v>3.1704905106372541E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12">
         <v>9740</v>
       </c>
       <c r="H12">
-        <v>11195.77072864323</v>
+        <v>11195.770728643231</v>
       </c>
       <c r="I12">
-        <v>1455.770728643225</v>
+        <v>1455.7707286432251</v>
       </c>
       <c r="J12">
-        <v>0.1494631138237398</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>0.14946311382373981</v>
+      </c>
+      <c r="K12">
+        <v>0.69422665716322163</v>
+      </c>
+      <c r="L12">
+        <v>0.68530150753768893</v>
+      </c>
+      <c r="M12">
+        <v>0.63102328939888375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G13">
         <v>2440</v>
       </c>
       <c r="H13">
-        <v>2945.175251256281</v>
+        <v>2945.1752512562812</v>
       </c>
       <c r="I13">
-        <v>505.1752512562812</v>
+        <v>505.17525125628117</v>
       </c>
       <c r="J13">
         <v>0.2070390374001152</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13">
+        <v>0.17391304347826089</v>
+      </c>
+      <c r="L13">
+        <v>0.1802763819095477</v>
+      </c>
+      <c r="M13">
+        <v>0.21897496803479891</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G14">
-        <v>570</v>
+        <v>7700</v>
       </c>
       <c r="H14">
-        <v>869.5384466395416</v>
+        <v>8607.4536122409099</v>
       </c>
       <c r="I14">
-        <v>299.5384466395416</v>
+        <v>907.45361224090993</v>
       </c>
       <c r="J14">
-        <v>0.5255060467360378</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>0.11785111847284541</v>
+      </c>
+      <c r="K14">
+        <v>0.16882262661697001</v>
+      </c>
+      <c r="L14">
+        <v>0.17063722641874809</v>
+      </c>
+      <c r="M14">
+        <v>0.18776197232379679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G15">
-        <v>7700</v>
+        <v>570</v>
       </c>
       <c r="H15">
-        <v>8607.45361224091</v>
+        <v>869.53844663954158</v>
       </c>
       <c r="I15">
-        <v>907.4536122409099</v>
+        <v>299.53844663954158</v>
       </c>
       <c r="J15">
-        <v>0.1178511184728454</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>0.52550604673603785</v>
+      </c>
+      <c r="K15">
+        <v>1.249725937294453E-2</v>
+      </c>
+      <c r="L15">
+        <v>1.7238039899283179E-2</v>
+      </c>
+      <c r="M15">
+        <v>6.1977746045839339E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G16">
         <v>29200</v>
       </c>
       <c r="H16">
-        <v>32680.96746077867</v>
+        <v>32680.967460778669</v>
       </c>
       <c r="I16">
-        <v>3480.967460778669</v>
+        <v>3480.9674607786692</v>
       </c>
       <c r="J16">
         <v>0.1192112144102284</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16">
+        <v>0.64021048015786008</v>
+      </c>
+      <c r="L16">
+        <v>0.64787914003486446</v>
+      </c>
+      <c r="M16">
+        <v>0.72024983670156606</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G17">
         <v>8140</v>
       </c>
       <c r="H17">
-        <v>8285.04048034088</v>
+        <v>8285.0404803408801</v>
       </c>
       <c r="I17">
-        <v>145.0404803408801</v>
+        <v>145.04048034088009</v>
       </c>
       <c r="J17">
-        <v>0.01781824082811795</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>1.7818240828117948E-2</v>
+      </c>
+      <c r="K17">
+        <v>0.17846963385222539</v>
+      </c>
+      <c r="L17">
+        <v>0.16424559364710431</v>
+      </c>
+      <c r="M17">
+        <v>3.0010444928797859E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G18">
-        <v>160</v>
+        <v>4810</v>
       </c>
       <c r="H18">
-        <v>602.9863098942116</v>
+        <v>7463.3777224642181</v>
       </c>
       <c r="I18">
-        <v>442.9863098942116</v>
+        <v>2653.3777224642181</v>
       </c>
       <c r="J18">
-        <v>2.768664436838822</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>0.55163778013809106</v>
+      </c>
+      <c r="K18">
+        <v>0.32654446707399859</v>
+      </c>
+      <c r="L18">
+        <v>0.4082140634723086</v>
+      </c>
+      <c r="M18">
+        <v>0.7467992464014126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G19">
-        <v>4810</v>
+        <v>160</v>
       </c>
       <c r="H19">
-        <v>7463.377722464218</v>
+        <v>602.98630989421156</v>
       </c>
       <c r="I19">
-        <v>2653.377722464218</v>
+        <v>442.98630989421162</v>
       </c>
       <c r="J19">
-        <v>0.5516377801380911</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>2.7686644368388218</v>
+      </c>
+      <c r="K19">
+        <v>1.0862186014935511E-2</v>
+      </c>
+      <c r="L19">
+        <v>3.2980709396390723E-2</v>
+      </c>
+      <c r="M19">
+        <v>0.1246795130577573</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G20">
         <v>7400</v>
       </c>
       <c r="H20">
-        <v>7827.444928438092</v>
+        <v>7827.4449284380917</v>
       </c>
       <c r="I20">
-        <v>427.4449284380917</v>
+        <v>427.44492843809172</v>
       </c>
       <c r="J20">
-        <v>0.05776282816730968</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>5.7762828167309682E-2</v>
+      </c>
+      <c r="K20">
+        <v>0.50237610319076709</v>
+      </c>
+      <c r="L20">
+        <v>0.42812694461729978</v>
+      </c>
+      <c r="M20">
+        <v>0.1203053555975491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G21">
         <v>2360</v>
       </c>
       <c r="H21">
-        <v>2389.191039203478</v>
+        <v>2389.1910392034779</v>
       </c>
       <c r="I21">
-        <v>29.19103920347789</v>
+        <v>29.191039203477889</v>
       </c>
       <c r="J21">
-        <v>0.01236908440825334</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>1.236908440825334E-2</v>
+      </c>
+      <c r="K21">
+        <v>0.16021724372029869</v>
+      </c>
+      <c r="L21">
+        <v>0.1306782825140009</v>
+      </c>
+      <c r="M21">
+        <v>8.2158849432811404E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G22">
-        <v>9830</v>
+        <v>83510</v>
       </c>
       <c r="H22">
-        <v>8739.664094232297</v>
+        <v>85951.422745735385</v>
       </c>
       <c r="I22">
-        <v>-1090.335905767703</v>
+        <v>2441.422745735385</v>
       </c>
       <c r="J22">
-        <v>-0.1109192172703665</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>2.9235094548382041E-2</v>
+      </c>
+      <c r="K22">
+        <v>0.72165572070515038</v>
+      </c>
+      <c r="L22">
+        <v>0.71502843216896994</v>
+      </c>
+      <c r="M22">
+        <v>0.5441102620315087</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G23">
-        <v>83510</v>
+        <v>9830</v>
       </c>
       <c r="H23">
-        <v>85951.42274573538</v>
+        <v>8739.6640942322974</v>
       </c>
       <c r="I23">
-        <v>2441.422745735385</v>
+        <v>-1090.335905767703</v>
       </c>
       <c r="J23">
-        <v>0.02923509454838204</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>-0.11091921727036649</v>
+      </c>
+      <c r="K23">
+        <v>8.4946422398893884E-2</v>
+      </c>
+      <c r="L23">
+        <v>7.2705117790414012E-2</v>
+      </c>
+      <c r="M23">
+        <v>-0.24299886466853141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G24">
         <v>14290</v>
       </c>
       <c r="H24">
-        <v>16063.4049553208</v>
+        <v>16063.404955320801</v>
       </c>
       <c r="I24">
         <v>1773.404955320801</v>
@@ -3240,374 +4033,482 @@
       <c r="J24">
         <v>0.1241011165374948</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24">
+        <v>0.12348772900103699</v>
+      </c>
+      <c r="L24">
+        <v>0.13363119415109601</v>
+      </c>
+      <c r="M24">
+        <v>0.39523177074232158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G25">
         <v>8090</v>
       </c>
       <c r="H25">
-        <v>9452.508204711527</v>
+        <v>9452.5082047115266</v>
       </c>
       <c r="I25">
         <v>1362.508204711527</v>
       </c>
       <c r="J25">
-        <v>0.1684188139322035</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>0.16841881393220351</v>
+      </c>
+      <c r="K25">
+        <v>6.9910127894918767E-2</v>
+      </c>
+      <c r="L25">
+        <v>7.8635255889519959E-2</v>
+      </c>
+      <c r="M25">
+        <v>0.30365683189470111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G26">
-        <v>2670</v>
+        <v>24380</v>
       </c>
       <c r="H26">
-        <v>2795.482474226756</v>
+        <v>28420.738487972219</v>
       </c>
       <c r="I26">
-        <v>125.4824742267556</v>
+        <v>4040.738487972219</v>
       </c>
       <c r="J26">
-        <v>0.04699718135833542</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>0.16573988876014031</v>
+      </c>
+      <c r="K26">
+        <v>0.1449809705042816</v>
+      </c>
+      <c r="L26">
+        <v>0.16420389461626411</v>
+      </c>
+      <c r="M26">
+        <v>0.82095458918573838</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G27">
-        <v>24380</v>
+        <v>2670</v>
       </c>
       <c r="H27">
-        <v>28420.73848797222</v>
+        <v>2795.482474226756</v>
       </c>
       <c r="I27">
-        <v>4040.738487972219</v>
+        <v>125.4824742267556</v>
       </c>
       <c r="J27">
-        <v>0.1657398887601403</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>4.6997181358335423E-2</v>
+      </c>
+      <c r="K27">
+        <v>1.587773549000952E-2</v>
+      </c>
+      <c r="L27">
+        <v>1.6151202749140611E-2</v>
+      </c>
+      <c r="M27">
+        <v>2.5494204434529689E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G28">
         <v>122010</v>
       </c>
       <c r="H28">
-        <v>122029.7491408939</v>
+        <v>122029.74914089389</v>
       </c>
       <c r="I28">
         <v>19.74914089392405</v>
       </c>
       <c r="J28">
-        <v>0.0001618649364308176</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>1.6186493643081761E-4</v>
+      </c>
+      <c r="K28">
+        <v>0.72555899143672697</v>
+      </c>
+      <c r="L28">
+        <v>0.70504009163803227</v>
+      </c>
+      <c r="M28">
+        <v>4.0124219613823604E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G29">
         <v>19100</v>
       </c>
       <c r="H29">
-        <v>19836.02989690712</v>
+        <v>19836.029896907119</v>
       </c>
       <c r="I29">
-        <v>736.0298969071191</v>
+        <v>736.02989690711911</v>
       </c>
       <c r="J29">
-        <v>0.03853559669670781</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>3.8535596696707808E-2</v>
+      </c>
+      <c r="K29">
+        <v>0.1135823025689819</v>
+      </c>
+      <c r="L29">
+        <v>0.114604810996563</v>
+      </c>
+      <c r="M29">
+        <v>0.1495387844183495</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G30">
-        <v>210</v>
+        <v>15400</v>
       </c>
       <c r="H30">
-        <v>822.964234104015</v>
+        <v>19646.96893063571</v>
       </c>
       <c r="I30">
-        <v>612.964234104015</v>
+        <v>4246.9689306357141</v>
       </c>
       <c r="J30">
-        <v>2.918877305257214</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>0.2757772032880334</v>
+      </c>
+      <c r="K30">
+        <v>0.15305108328364139</v>
+      </c>
+      <c r="L30">
+        <v>0.17033959537572141</v>
+      </c>
+      <c r="M30">
+        <v>0.28851691104862159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G31">
-        <v>15400</v>
+        <v>210</v>
       </c>
       <c r="H31">
-        <v>19646.96893063571</v>
+        <v>822.96423410401496</v>
       </c>
       <c r="I31">
-        <v>4246.968930635714</v>
+        <v>612.96423410401496</v>
       </c>
       <c r="J31">
-        <v>0.2757772032880334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>2.9188773052572139</v>
+      </c>
+      <c r="K31">
+        <v>2.0870602265951098E-3</v>
+      </c>
+      <c r="L31">
+        <v>7.1351156069361437E-3</v>
+      </c>
+      <c r="M31">
+        <v>4.1641591990761853E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D32">
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G32">
         <v>28370</v>
       </c>
       <c r="H32">
-        <v>29126.68352601153</v>
+        <v>29126.683526011529</v>
       </c>
       <c r="I32">
         <v>756.6835260115331</v>
       </c>
       <c r="J32">
-        <v>0.02667196073357537</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>2.6671960733575369E-2</v>
+      </c>
+      <c r="K32">
+        <v>0.281951898230968</v>
+      </c>
+      <c r="L32">
+        <v>0.25252890173410381</v>
+      </c>
+      <c r="M32">
+        <v>5.1405130843174773E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D33">
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G33">
         <v>56640</v>
       </c>
       <c r="H33">
-        <v>65743.38330924875</v>
+        <v>65743.383309248748</v>
       </c>
       <c r="I33">
-        <v>9103.383309248748</v>
+        <v>9103.3833092487475</v>
       </c>
       <c r="J33">
-        <v>0.1607235753751544</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>0.16072357537515439</v>
+      </c>
+      <c r="K33">
+        <v>0.56290995825879542</v>
+      </c>
+      <c r="L33">
+        <v>0.56999638728323854</v>
+      </c>
+      <c r="M33">
+        <v>0.61843636611744168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D34">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="H34">
-        <v>50.72146917358625</v>
+        <v>6147.4420638390802</v>
       </c>
       <c r="I34">
-        <v>50.72146917358625</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>1547.44206383908</v>
+      </c>
+      <c r="J34">
+        <v>0.33640044866066959</v>
+      </c>
+      <c r="K34">
+        <v>7.1362085013962143E-2</v>
+      </c>
+      <c r="L34">
+        <v>8.8325317009182183E-2</v>
+      </c>
+      <c r="M34">
+        <v>0.30105876728386788</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D35">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G35">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>6147.44206383908</v>
+        <v>50.72146917358625</v>
       </c>
       <c r="I35">
-        <v>1547.44206383908</v>
-      </c>
-      <c r="J35">
-        <v>0.3364004486606696</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>50.72146917358625</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>7.2875674099980242E-4</v>
+      </c>
+      <c r="M35">
+        <v>9.8679901115926588E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D36">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G36">
         <v>10540</v>
@@ -3619,164 +4520,218 @@
         <v>1825.89418452115</v>
       </c>
       <c r="J36">
-        <v>0.1732347423644355</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>0.17323474236443551</v>
+      </c>
+      <c r="K36">
+        <v>0.1635122556624263</v>
+      </c>
+      <c r="L36">
+        <v>0.17767089345576359</v>
+      </c>
+      <c r="M36">
+        <v>0.35523233161890089</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D37">
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F37" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G37">
         <v>49320</v>
       </c>
       <c r="H37">
-        <v>51035.94228246618</v>
+        <v>51035.942282466181</v>
       </c>
       <c r="I37">
         <v>1715.942282466181</v>
       </c>
       <c r="J37">
-        <v>0.03479201708163385</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>3.4792017081633847E-2</v>
+      </c>
+      <c r="K37">
+        <v>0.76512565932361154</v>
+      </c>
+      <c r="L37">
+        <v>0.73327503279405437</v>
+      </c>
+      <c r="M37">
+        <v>0.33384091098563862</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D38">
         <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="H38">
-        <v>129.8034497444613</v>
+        <v>3914.0732538330271</v>
       </c>
       <c r="I38">
-        <v>129.8034497444613</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>2264.0732538330271</v>
+      </c>
+      <c r="J38">
+        <v>1.3721656083836531</v>
+      </c>
+      <c r="K38">
+        <v>3.6609718216108277E-2</v>
+      </c>
+      <c r="L38">
+        <v>8.3475298126064246E-2</v>
+      </c>
+      <c r="M38">
+        <v>1.2446801835255741</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D39">
         <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G39">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>3914.073253833027</v>
+        <v>129.80344974446129</v>
       </c>
       <c r="I39">
-        <v>2264.073253833027</v>
-      </c>
-      <c r="J39">
-        <v>1.372165608383653</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>129.80344974446129</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>2.7683134582623049E-3</v>
+      </c>
+      <c r="M39">
+        <v>7.135978545599822E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D40">
         <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G40">
         <v>4990</v>
       </c>
       <c r="H40">
-        <v>5821.185477001693</v>
+        <v>5821.1854770016926</v>
       </c>
       <c r="I40">
-        <v>831.1854770016926</v>
+        <v>831.18547700169256</v>
       </c>
       <c r="J40">
-        <v>0.1665702358720827</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>0.16657023587208269</v>
+      </c>
+      <c r="K40">
+        <v>0.1107166629687153</v>
+      </c>
+      <c r="L40">
+        <v>0.12414821124361131</v>
+      </c>
+      <c r="M40">
+        <v>0.45694638647701452</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D41">
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G41">
         <v>38430</v>
       </c>
       <c r="H41">
-        <v>37023.93781942083</v>
+        <v>37023.937819420833</v>
       </c>
       <c r="I41">
-        <v>-1406.062180579174</v>
+        <v>-1406.0621805791741</v>
       </c>
       <c r="J41">
-        <v>-0.03658761854226319</v>
+        <v>-3.6587618542263188E-2</v>
+      </c>
+      <c r="K41">
+        <v>0.85267361881517634</v>
+      </c>
+      <c r="L41">
+        <v>0.78960817717206211</v>
+      </c>
+      <c r="M41">
+        <v>-0.77298635545858663</v>
       </c>
     </row>
   </sheetData>
